--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/08,26/25,08,26 ПОКОМ КИ/дв 25,08,26 млрсч пок ки.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/08,26/25,08,26 ПОКОМ КИ/дв 25,08,26 млрсч пок ки.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\08,26\25,08,26 ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26621760-9DD6-4965-BE49-C1A30A1C10CA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BFF5C6C-AEF5-4498-9C0E-BD7B2A17EA24}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AH$133</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1041,7 +1041,8 @@
     <col min="23" max="32" width="6" customWidth="1"/>
     <col min="33" max="33" width="40.85546875" customWidth="1"/>
     <col min="34" max="34" width="7" customWidth="1"/>
-    <col min="35" max="46" width="3" customWidth="1"/>
+    <col min="35" max="35" width="7.7109375" customWidth="1"/>
+    <col min="36" max="46" width="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:46" x14ac:dyDescent="0.25">
@@ -1442,7 +1443,10 @@
         <f>SUM(AH6:AH499)</f>
         <v>11032</v>
       </c>
-      <c r="AI5" s="1"/>
+      <c r="AI5" s="4">
+        <f>SUM(AI6:AI499)</f>
+        <v>3639.9070000000006</v>
+      </c>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="1"/>
       <c r="AL5" s="1"/>
@@ -1553,7 +1557,10 @@
         <f>ROUND(G6*T6,0)</f>
         <v>325</v>
       </c>
-      <c r="AI6" s="1"/>
+      <c r="AI6" s="1">
+        <f>R6*G6</f>
+        <v>62.169200000000004</v>
+      </c>
       <c r="AJ6" s="1"/>
       <c r="AK6" s="1"/>
       <c r="AL6" s="1"/>
@@ -1664,7 +1671,10 @@
         <f t="shared" ref="AH7:AH70" si="7">ROUND(G7*T7,0)</f>
         <v>415</v>
       </c>
-      <c r="AI7" s="1"/>
+      <c r="AI7" s="1">
+        <f t="shared" ref="AI7:AI70" si="8">R7*G7</f>
+        <v>172.14420000000001</v>
+      </c>
       <c r="AJ7" s="1"/>
       <c r="AK7" s="1"/>
       <c r="AL7" s="1"/>
@@ -1775,7 +1785,10 @@
         <f t="shared" si="7"/>
         <v>291</v>
       </c>
-      <c r="AI8" s="1"/>
+      <c r="AI8" s="1">
+        <f t="shared" si="8"/>
+        <v>164.05779999999999</v>
+      </c>
       <c r="AJ8" s="1"/>
       <c r="AK8" s="1"/>
       <c r="AL8" s="1"/>
@@ -1837,7 +1850,7 @@
       </c>
       <c r="S9" s="5"/>
       <c r="T9" s="5">
-        <f t="shared" ref="T9:T65" si="8">S9</f>
+        <f t="shared" ref="T9:T65" si="9">S9</f>
         <v>0</v>
       </c>
       <c r="U9" s="1">
@@ -1885,7 +1898,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AI9" s="1"/>
+      <c r="AI9" s="1">
+        <f t="shared" si="8"/>
+        <v>1.04</v>
+      </c>
       <c r="AJ9" s="1"/>
       <c r="AK9" s="1"/>
       <c r="AL9" s="1"/>
@@ -1947,7 +1963,7 @@
       </c>
       <c r="S10" s="5"/>
       <c r="T10" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U10" s="1">
@@ -1993,7 +2009,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AI10" s="1"/>
+      <c r="AI10" s="1">
+        <f t="shared" si="8"/>
+        <v>18.990000000000002</v>
+      </c>
       <c r="AJ10" s="1"/>
       <c r="AK10" s="1"/>
       <c r="AL10" s="1"/>
@@ -2055,7 +2074,7 @@
       </c>
       <c r="S11" s="5"/>
       <c r="T11" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U11" s="1">
@@ -2101,7 +2120,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AI11" s="1"/>
+      <c r="AI11" s="1">
+        <f t="shared" si="8"/>
+        <v>17.73</v>
+      </c>
       <c r="AJ11" s="1"/>
       <c r="AK11" s="1"/>
       <c r="AL11" s="1"/>
@@ -2151,7 +2173,7 @@
       </c>
       <c r="S12" s="11"/>
       <c r="T12" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U12" s="1" t="e">
@@ -2199,7 +2221,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AI12" s="1"/>
+      <c r="AI12" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AJ12" s="1"/>
       <c r="AK12" s="1"/>
       <c r="AL12" s="1"/>
@@ -2311,7 +2336,10 @@
         <f t="shared" si="7"/>
         <v>15</v>
       </c>
-      <c r="AI13" s="1"/>
+      <c r="AI13" s="1">
+        <f t="shared" si="8"/>
+        <v>8.1</v>
+      </c>
       <c r="AJ13" s="1"/>
       <c r="AK13" s="1"/>
       <c r="AL13" s="1"/>
@@ -2372,11 +2400,11 @@
         <v>31.2</v>
       </c>
       <c r="S14" s="5">
-        <f t="shared" ref="S14:S21" si="9">11*R14-Q14-P14-O14-F14</f>
+        <f t="shared" ref="S14:S21" si="10">11*R14-Q14-P14-O14-F14</f>
         <v>160.20599999999999</v>
       </c>
       <c r="T14" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>160.20599999999999</v>
       </c>
       <c r="U14" s="1">
@@ -2422,7 +2450,10 @@
         <f t="shared" si="7"/>
         <v>27</v>
       </c>
-      <c r="AI14" s="1"/>
+      <c r="AI14" s="1">
+        <f t="shared" si="8"/>
+        <v>5.3040000000000003</v>
+      </c>
       <c r="AJ14" s="1"/>
       <c r="AK14" s="1"/>
       <c r="AL14" s="1"/>
@@ -2483,11 +2514,11 @@
         <v>60.460999999999999</v>
       </c>
       <c r="S15" s="5">
+        <f t="shared" si="10"/>
+        <v>138.692834</v>
+      </c>
+      <c r="T15" s="5">
         <f t="shared" si="9"/>
-        <v>138.692834</v>
-      </c>
-      <c r="T15" s="5">
-        <f t="shared" si="8"/>
         <v>138.692834</v>
       </c>
       <c r="U15" s="1">
@@ -2533,7 +2564,10 @@
         <f t="shared" si="7"/>
         <v>139</v>
       </c>
-      <c r="AI15" s="1"/>
+      <c r="AI15" s="1">
+        <f t="shared" si="8"/>
+        <v>60.460999999999999</v>
+      </c>
       <c r="AJ15" s="1"/>
       <c r="AK15" s="1"/>
       <c r="AL15" s="1"/>
@@ -2646,7 +2680,10 @@
         <f t="shared" si="7"/>
         <v>947</v>
       </c>
-      <c r="AI16" s="1"/>
+      <c r="AI16" s="1">
+        <f t="shared" si="8"/>
+        <v>400.47460000000001</v>
+      </c>
       <c r="AJ16" s="1"/>
       <c r="AK16" s="1"/>
       <c r="AL16" s="1"/>
@@ -2707,11 +2744,11 @@
         <v>10.763999999999999</v>
       </c>
       <c r="S17" s="5">
+        <f t="shared" si="10"/>
+        <v>41.762999999999991</v>
+      </c>
+      <c r="T17" s="5">
         <f t="shared" si="9"/>
-        <v>41.762999999999991</v>
-      </c>
-      <c r="T17" s="5">
-        <f t="shared" si="8"/>
         <v>41.762999999999991</v>
       </c>
       <c r="U17" s="1">
@@ -2757,7 +2794,10 @@
         <f t="shared" si="7"/>
         <v>42</v>
       </c>
-      <c r="AI17" s="1"/>
+      <c r="AI17" s="1">
+        <f t="shared" si="8"/>
+        <v>10.763999999999999</v>
+      </c>
       <c r="AJ17" s="1"/>
       <c r="AK17" s="1"/>
       <c r="AL17" s="1"/>
@@ -2818,11 +2858,11 @@
         <v>6.4992000000000001</v>
       </c>
       <c r="S18" s="5">
+        <f t="shared" si="10"/>
+        <v>11.766200000000005</v>
+      </c>
+      <c r="T18" s="5">
         <f t="shared" si="9"/>
-        <v>11.766200000000005</v>
-      </c>
-      <c r="T18" s="5">
-        <f t="shared" si="8"/>
         <v>11.766200000000005</v>
       </c>
       <c r="U18" s="1">
@@ -2868,7 +2908,10 @@
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
-      <c r="AI18" s="1"/>
+      <c r="AI18" s="1">
+        <f t="shared" si="8"/>
+        <v>6.4992000000000001</v>
+      </c>
       <c r="AJ18" s="1"/>
       <c r="AK18" s="1"/>
       <c r="AL18" s="1"/>
@@ -2929,11 +2972,11 @@
         <v>6.3506</v>
       </c>
       <c r="S19" s="5">
+        <f t="shared" si="10"/>
+        <v>28.187799999999985</v>
+      </c>
+      <c r="T19" s="5">
         <f t="shared" si="9"/>
-        <v>28.187799999999985</v>
-      </c>
-      <c r="T19" s="5">
-        <f t="shared" si="8"/>
         <v>28.187799999999985</v>
       </c>
       <c r="U19" s="1">
@@ -2979,7 +3022,10 @@
         <f t="shared" si="7"/>
         <v>28</v>
       </c>
-      <c r="AI19" s="1"/>
+      <c r="AI19" s="1">
+        <f t="shared" si="8"/>
+        <v>6.3506</v>
+      </c>
       <c r="AJ19" s="1"/>
       <c r="AK19" s="1"/>
       <c r="AL19" s="1"/>
@@ -3040,11 +3086,11 @@
         <v>72.000399999999999</v>
       </c>
       <c r="S20" s="5">
+        <f t="shared" si="10"/>
+        <v>227.1958740000004</v>
+      </c>
+      <c r="T20" s="5">
         <f t="shared" si="9"/>
-        <v>227.1958740000004</v>
-      </c>
-      <c r="T20" s="5">
-        <f t="shared" si="8"/>
         <v>227.1958740000004</v>
       </c>
       <c r="U20" s="1">
@@ -3090,7 +3136,10 @@
         <f t="shared" si="7"/>
         <v>227</v>
       </c>
-      <c r="AI20" s="1"/>
+      <c r="AI20" s="1">
+        <f t="shared" si="8"/>
+        <v>72.000399999999999</v>
+      </c>
       <c r="AJ20" s="1"/>
       <c r="AK20" s="1"/>
       <c r="AL20" s="1"/>
@@ -3151,11 +3200,11 @@
         <v>16.8612</v>
       </c>
       <c r="S21" s="5">
+        <f t="shared" si="10"/>
+        <v>43.753399999999942</v>
+      </c>
+      <c r="T21" s="5">
         <f t="shared" si="9"/>
-        <v>43.753399999999942</v>
-      </c>
-      <c r="T21" s="5">
-        <f t="shared" si="8"/>
         <v>43.753399999999942</v>
       </c>
       <c r="U21" s="1">
@@ -3201,7 +3250,10 @@
         <f t="shared" si="7"/>
         <v>44</v>
       </c>
-      <c r="AI21" s="1"/>
+      <c r="AI21" s="1">
+        <f t="shared" si="8"/>
+        <v>16.8612</v>
+      </c>
       <c r="AJ21" s="1"/>
       <c r="AK21" s="1"/>
       <c r="AL21" s="1"/>
@@ -3313,7 +3365,10 @@
         <f t="shared" si="7"/>
         <v>70</v>
       </c>
-      <c r="AI22" s="1"/>
+      <c r="AI22" s="1">
+        <f t="shared" si="8"/>
+        <v>41.7134</v>
+      </c>
       <c r="AJ22" s="1"/>
       <c r="AK22" s="1"/>
       <c r="AL22" s="1"/>
@@ -3378,7 +3433,7 @@
         <v>55.860000000000014</v>
       </c>
       <c r="T23" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>55.860000000000014</v>
       </c>
       <c r="U23" s="1">
@@ -3424,7 +3479,10 @@
         <f t="shared" si="7"/>
         <v>56</v>
       </c>
-      <c r="AI23" s="1"/>
+      <c r="AI23" s="1">
+        <f t="shared" si="8"/>
+        <v>9.031600000000001</v>
+      </c>
       <c r="AJ23" s="1"/>
       <c r="AK23" s="1"/>
       <c r="AL23" s="1"/>
@@ -3536,7 +3594,10 @@
         <f t="shared" si="7"/>
         <v>70</v>
       </c>
-      <c r="AI24" s="1"/>
+      <c r="AI24" s="1">
+        <f t="shared" si="8"/>
+        <v>37.118400000000001</v>
+      </c>
       <c r="AJ24" s="1"/>
       <c r="AK24" s="1"/>
       <c r="AL24" s="1"/>
@@ -3596,7 +3657,7 @@
       </c>
       <c r="S25" s="11"/>
       <c r="T25" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U25" s="1">
@@ -3642,7 +3703,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AI25" s="1"/>
+      <c r="AI25" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AJ25" s="1"/>
       <c r="AK25" s="1"/>
       <c r="AL25" s="1"/>
@@ -3692,7 +3756,7 @@
       </c>
       <c r="S26" s="11"/>
       <c r="T26" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U26" s="1" t="e">
@@ -3740,7 +3804,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AI26" s="1"/>
+      <c r="AI26" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AJ26" s="1"/>
       <c r="AK26" s="1"/>
       <c r="AL26" s="1"/>
@@ -3801,11 +3868,11 @@
         <v>57.585799999999992</v>
       </c>
       <c r="S27" s="5">
-        <f t="shared" ref="S27:S33" si="10">11*R27-Q27-P27-O27-F27</f>
+        <f t="shared" ref="S27:S33" si="11">11*R27-Q27-P27-O27-F27</f>
         <v>332.22768399999961</v>
       </c>
       <c r="T27" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>332.22768399999961</v>
       </c>
       <c r="U27" s="1">
@@ -3851,7 +3918,10 @@
         <f t="shared" si="7"/>
         <v>332</v>
       </c>
-      <c r="AI27" s="1"/>
+      <c r="AI27" s="1">
+        <f t="shared" si="8"/>
+        <v>57.585799999999992</v>
+      </c>
       <c r="AJ27" s="1"/>
       <c r="AK27" s="1"/>
       <c r="AL27" s="1"/>
@@ -3915,7 +3985,7 @@
         <v>150</v>
       </c>
       <c r="T28" s="5">
-        <f t="shared" ref="T28:T30" si="11">S28*0.7</f>
+        <f t="shared" ref="T28:T30" si="12">S28*0.7</f>
         <v>105</v>
       </c>
       <c r="U28" s="1">
@@ -3961,7 +4031,10 @@
         <f t="shared" si="7"/>
         <v>105</v>
       </c>
-      <c r="AI28" s="1"/>
+      <c r="AI28" s="1">
+        <f t="shared" si="8"/>
+        <v>-0.79859999999999998</v>
+      </c>
       <c r="AJ28" s="1"/>
       <c r="AK28" s="1"/>
       <c r="AL28" s="1"/>
@@ -4027,7 +4100,7 @@
         <v>200</v>
       </c>
       <c r="T29" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>140</v>
       </c>
       <c r="U29" s="1">
@@ -4073,7 +4146,10 @@
         <f t="shared" si="7"/>
         <v>140</v>
       </c>
-      <c r="AI29" s="1"/>
+      <c r="AI29" s="1">
+        <f t="shared" si="8"/>
+        <v>72.658000000000001</v>
+      </c>
       <c r="AJ29" s="1"/>
       <c r="AK29" s="1"/>
       <c r="AL29" s="1"/>
@@ -4137,7 +4213,7 @@
         <v>400</v>
       </c>
       <c r="T30" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>280</v>
       </c>
       <c r="U30" s="1">
@@ -4183,7 +4259,10 @@
         <f t="shared" si="7"/>
         <v>280</v>
       </c>
-      <c r="AI30" s="1"/>
+      <c r="AI30" s="1">
+        <f t="shared" si="8"/>
+        <v>85.760400000000004</v>
+      </c>
       <c r="AJ30" s="1"/>
       <c r="AK30" s="1"/>
       <c r="AL30" s="1"/>
@@ -4245,7 +4324,7 @@
         <v>20</v>
       </c>
       <c r="T31" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="U31" s="1">
@@ -4291,7 +4370,10 @@
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
-      <c r="AI31" s="1"/>
+      <c r="AI31" s="1">
+        <f t="shared" si="8"/>
+        <v>5.5952000000000002</v>
+      </c>
       <c r="AJ31" s="1"/>
       <c r="AK31" s="1"/>
       <c r="AL31" s="1"/>
@@ -4356,7 +4438,7 @@
         <v>113.1324</v>
       </c>
       <c r="T32" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>113.1324</v>
       </c>
       <c r="U32" s="1">
@@ -4402,7 +4484,10 @@
         <f t="shared" si="7"/>
         <v>113</v>
       </c>
-      <c r="AI32" s="1"/>
+      <c r="AI32" s="1">
+        <f t="shared" si="8"/>
+        <v>18.741599999999998</v>
+      </c>
       <c r="AJ32" s="1"/>
       <c r="AK32" s="1"/>
       <c r="AL32" s="1"/>
@@ -4463,11 +4548,11 @@
         <v>12.454000000000001</v>
       </c>
       <c r="S33" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>62.060200000000009</v>
       </c>
       <c r="T33" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>62.060200000000009</v>
       </c>
       <c r="U33" s="1">
@@ -4513,7 +4598,10 @@
         <f t="shared" si="7"/>
         <v>62</v>
       </c>
-      <c r="AI33" s="1"/>
+      <c r="AI33" s="1">
+        <f t="shared" si="8"/>
+        <v>12.454000000000001</v>
+      </c>
       <c r="AJ33" s="1"/>
       <c r="AK33" s="1"/>
       <c r="AL33" s="1"/>
@@ -4573,7 +4661,7 @@
       </c>
       <c r="S34" s="11"/>
       <c r="T34" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U34" s="1">
@@ -4619,7 +4707,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AI34" s="1"/>
+      <c r="AI34" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AJ34" s="1"/>
       <c r="AK34" s="1"/>
       <c r="AL34" s="1"/>
@@ -4683,7 +4774,7 @@
         <v>30</v>
       </c>
       <c r="T35" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>30</v>
       </c>
       <c r="U35" s="1">
@@ -4729,7 +4820,10 @@
         <f t="shared" si="7"/>
         <v>30</v>
       </c>
-      <c r="AI35" s="1"/>
+      <c r="AI35" s="1">
+        <f t="shared" si="8"/>
+        <v>10.155800000000001</v>
+      </c>
       <c r="AJ35" s="1"/>
       <c r="AK35" s="1"/>
       <c r="AL35" s="1"/>
@@ -4839,7 +4933,10 @@
         <f t="shared" si="7"/>
         <v>140</v>
       </c>
-      <c r="AI36" s="1"/>
+      <c r="AI36" s="1">
+        <f t="shared" si="8"/>
+        <v>45.760000000000005</v>
+      </c>
       <c r="AJ36" s="1"/>
       <c r="AK36" s="1"/>
       <c r="AL36" s="1"/>
@@ -4900,11 +4997,11 @@
         <v>51.6</v>
       </c>
       <c r="S37" s="5">
-        <f t="shared" ref="S37:S41" si="12">11*R37-Q37-P37-O37-F37</f>
+        <f t="shared" ref="S37:S41" si="13">11*R37-Q37-P37-O37-F37</f>
         <v>260.89800000000002</v>
       </c>
       <c r="T37" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>260.89800000000002</v>
       </c>
       <c r="U37" s="1">
@@ -4950,7 +5047,10 @@
         <f t="shared" si="7"/>
         <v>117</v>
       </c>
-      <c r="AI37" s="1"/>
+      <c r="AI37" s="1">
+        <f t="shared" si="8"/>
+        <v>23.220000000000002</v>
+      </c>
       <c r="AJ37" s="1"/>
       <c r="AK37" s="1"/>
       <c r="AL37" s="1"/>
@@ -4996,7 +5096,7 @@
         <v>367</v>
       </c>
       <c r="L38" s="1">
-        <f t="shared" ref="L38:L69" si="13">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="14">E38-K38</f>
         <v>-222</v>
       </c>
       <c r="M38" s="1"/>
@@ -5009,7 +5109,7 @@
       </c>
       <c r="Q38" s="1"/>
       <c r="R38" s="1">
-        <f t="shared" ref="R38:R69" si="14">E38/5</f>
+        <f t="shared" ref="R38:R69" si="15">E38/5</f>
         <v>29</v>
       </c>
       <c r="S38" s="5">
@@ -5024,7 +5124,7 @@
         <v>3.0172413793103448</v>
       </c>
       <c r="V38" s="1">
-        <f t="shared" ref="V38:V69" si="15">(F38+O38+P38+Q38)/R38</f>
+        <f t="shared" ref="V38:V69" si="16">(F38+O38+P38+Q38)/R38</f>
         <v>0.60344827586206895</v>
       </c>
       <c r="W38" s="1">
@@ -5062,7 +5162,10 @@
         <f t="shared" si="7"/>
         <v>28</v>
       </c>
-      <c r="AI38" s="1"/>
+      <c r="AI38" s="1">
+        <f t="shared" si="8"/>
+        <v>11.600000000000001</v>
+      </c>
       <c r="AJ38" s="1"/>
       <c r="AK38" s="1"/>
       <c r="AL38" s="1"/>
@@ -5108,7 +5211,7 @@
         <v>53</v>
       </c>
       <c r="L39" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-10</v>
       </c>
       <c r="M39" s="1"/>
@@ -5121,14 +5224,14 @@
       </c>
       <c r="Q39" s="1"/>
       <c r="R39" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>8.6</v>
       </c>
       <c r="S39" s="5">
         <v>30</v>
       </c>
       <c r="T39" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>30</v>
       </c>
       <c r="U39" s="1">
@@ -5136,7 +5239,7 @@
         <v>2.7906976744186047</v>
       </c>
       <c r="V39" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-0.69767441860465118</v>
       </c>
       <c r="W39" s="1">
@@ -5174,7 +5277,10 @@
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
-      <c r="AI39" s="1"/>
+      <c r="AI39" s="1">
+        <f t="shared" si="8"/>
+        <v>3.44</v>
+      </c>
       <c r="AJ39" s="1"/>
       <c r="AK39" s="1"/>
       <c r="AL39" s="1"/>
@@ -5220,7 +5326,7 @@
         <v>87.65</v>
       </c>
       <c r="L40" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-4.0740000000000123</v>
       </c>
       <c r="M40" s="1"/>
@@ -5231,14 +5337,14 @@
       <c r="P40" s="1"/>
       <c r="Q40" s="1"/>
       <c r="R40" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>16.715199999999999</v>
       </c>
       <c r="S40" s="5">
         <v>50</v>
       </c>
       <c r="T40" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>50</v>
       </c>
       <c r="U40" s="1">
@@ -5246,7 +5352,7 @@
         <v>4.4806523403847995</v>
       </c>
       <c r="V40" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1.4893629750167512</v>
       </c>
       <c r="W40" s="1">
@@ -5284,7 +5390,10 @@
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="AI40" s="1"/>
+      <c r="AI40" s="1">
+        <f t="shared" si="8"/>
+        <v>16.715199999999999</v>
+      </c>
       <c r="AJ40" s="1"/>
       <c r="AK40" s="1"/>
       <c r="AL40" s="1"/>
@@ -5330,7 +5439,7 @@
         <v>368</v>
       </c>
       <c r="L41" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>72</v>
       </c>
       <c r="M41" s="1"/>
@@ -5341,11 +5450,11 @@
       <c r="P41" s="1"/>
       <c r="Q41" s="1"/>
       <c r="R41" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>88</v>
       </c>
       <c r="S41" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>431.70000000000005</v>
       </c>
       <c r="T41" s="5">
@@ -5357,7 +5466,7 @@
         <v>10.299999999999999</v>
       </c>
       <c r="V41" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>6.0943181818181813</v>
       </c>
       <c r="W41" s="1">
@@ -5395,7 +5504,10 @@
         <f t="shared" si="7"/>
         <v>37</v>
       </c>
-      <c r="AI41" s="1"/>
+      <c r="AI41" s="1">
+        <f t="shared" si="8"/>
+        <v>8.8000000000000007</v>
+      </c>
       <c r="AJ41" s="1"/>
       <c r="AK41" s="1"/>
       <c r="AL41" s="1"/>
@@ -5441,7 +5553,7 @@
         <v>118</v>
       </c>
       <c r="L42" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-122</v>
       </c>
       <c r="M42" s="1"/>
@@ -5454,14 +5566,14 @@
       </c>
       <c r="Q42" s="1"/>
       <c r="R42" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-0.8</v>
       </c>
       <c r="S42" s="5">
         <v>100</v>
       </c>
       <c r="T42" s="5">
-        <f t="shared" ref="T42:T45" si="16">S42*0.7</f>
+        <f t="shared" ref="T42:T45" si="17">S42*0.7</f>
         <v>70</v>
       </c>
       <c r="U42" s="1">
@@ -5469,7 +5581,7 @@
         <v>-90</v>
       </c>
       <c r="V42" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-2.4999999999999911</v>
       </c>
       <c r="W42" s="1">
@@ -5507,7 +5619,10 @@
         <f t="shared" si="7"/>
         <v>25</v>
       </c>
-      <c r="AI42" s="1"/>
+      <c r="AI42" s="1">
+        <f t="shared" si="8"/>
+        <v>-0.27999999999999997</v>
+      </c>
       <c r="AJ42" s="1"/>
       <c r="AK42" s="1"/>
       <c r="AL42" s="1"/>
@@ -5553,7 +5668,7 @@
         <v>109.9</v>
       </c>
       <c r="L43" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4.6899999999999977</v>
       </c>
       <c r="M43" s="1"/>
@@ -5566,14 +5681,14 @@
       </c>
       <c r="Q43" s="1"/>
       <c r="R43" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>22.917999999999999</v>
       </c>
       <c r="S43" s="5">
         <v>60</v>
       </c>
       <c r="T43" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>42</v>
       </c>
       <c r="U43" s="1">
@@ -5581,7 +5696,7 @@
         <v>4.1776333013351952</v>
       </c>
       <c r="V43" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2.3450126538092331</v>
       </c>
       <c r="W43" s="1">
@@ -5619,7 +5734,10 @@
         <f t="shared" si="7"/>
         <v>42</v>
       </c>
-      <c r="AI43" s="1"/>
+      <c r="AI43" s="1">
+        <f t="shared" si="8"/>
+        <v>22.917999999999999</v>
+      </c>
       <c r="AJ43" s="1"/>
       <c r="AK43" s="1"/>
       <c r="AL43" s="1"/>
@@ -5665,7 +5783,7 @@
         <v>155</v>
       </c>
       <c r="L44" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-21</v>
       </c>
       <c r="M44" s="1"/>
@@ -5676,14 +5794,14 @@
       <c r="P44" s="1"/>
       <c r="Q44" s="1"/>
       <c r="R44" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>26.8</v>
       </c>
       <c r="S44" s="5">
         <v>150</v>
       </c>
       <c r="T44" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>105</v>
       </c>
       <c r="U44" s="1">
@@ -5691,7 +5809,7 @@
         <v>6.4925373134328357</v>
       </c>
       <c r="V44" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2.5746268656716418</v>
       </c>
       <c r="W44" s="1">
@@ -5729,7 +5847,10 @@
         <f t="shared" si="7"/>
         <v>42</v>
       </c>
-      <c r="AI44" s="1"/>
+      <c r="AI44" s="1">
+        <f t="shared" si="8"/>
+        <v>10.72</v>
+      </c>
       <c r="AJ44" s="1"/>
       <c r="AK44" s="1"/>
       <c r="AL44" s="1"/>
@@ -5775,7 +5896,7 @@
         <v>160</v>
       </c>
       <c r="L45" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-35</v>
       </c>
       <c r="M45" s="1"/>
@@ -5786,14 +5907,14 @@
       <c r="P45" s="1"/>
       <c r="Q45" s="1"/>
       <c r="R45" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>25</v>
       </c>
       <c r="S45" s="5">
         <v>150</v>
       </c>
       <c r="T45" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>105</v>
       </c>
       <c r="U45" s="1">
@@ -5801,7 +5922,7 @@
         <v>7</v>
       </c>
       <c r="V45" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2.8</v>
       </c>
       <c r="W45" s="1">
@@ -5839,7 +5960,10 @@
         <f t="shared" si="7"/>
         <v>42</v>
       </c>
-      <c r="AI45" s="1"/>
+      <c r="AI45" s="1">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
       <c r="AJ45" s="1"/>
       <c r="AK45" s="1"/>
       <c r="AL45" s="1"/>
@@ -5883,7 +6007,7 @@
         <v>29.2</v>
       </c>
       <c r="L46" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-29.916999999999998</v>
       </c>
       <c r="M46" s="9"/>
@@ -5894,12 +6018,12 @@
       <c r="P46" s="9"/>
       <c r="Q46" s="9"/>
       <c r="R46" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-0.1434</v>
       </c>
       <c r="S46" s="11"/>
       <c r="T46" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U46" s="1">
@@ -5907,7 +6031,7 @@
         <v>-15.341701534170154</v>
       </c>
       <c r="V46" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-15.341701534170154</v>
       </c>
       <c r="W46" s="9">
@@ -5945,7 +6069,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AI46" s="1"/>
+      <c r="AI46" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AJ46" s="1"/>
       <c r="AK46" s="1"/>
       <c r="AL46" s="1"/>
@@ -5991,7 +6118,7 @@
         <v>109.84</v>
       </c>
       <c r="L47" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>6.8310000000000031</v>
       </c>
       <c r="M47" s="1"/>
@@ -6004,14 +6131,14 @@
       </c>
       <c r="Q47" s="1"/>
       <c r="R47" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>23.334200000000003</v>
       </c>
       <c r="S47" s="5">
         <v>60</v>
       </c>
       <c r="T47" s="5">
-        <f t="shared" ref="T47:T49" si="17">S47*0.7</f>
+        <f t="shared" ref="T47:T49" si="18">S47*0.7</f>
         <v>42</v>
       </c>
       <c r="U47" s="1">
@@ -6019,7 +6146,7 @@
         <v>2.0553093742232429</v>
       </c>
       <c r="V47" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.25537622888292733</v>
       </c>
       <c r="W47" s="1">
@@ -6057,7 +6184,10 @@
         <f t="shared" si="7"/>
         <v>42</v>
       </c>
-      <c r="AI47" s="1"/>
+      <c r="AI47" s="1">
+        <f t="shared" si="8"/>
+        <v>23.334200000000003</v>
+      </c>
       <c r="AJ47" s="1"/>
       <c r="AK47" s="1"/>
       <c r="AL47" s="1"/>
@@ -6103,7 +6233,7 @@
         <v>362</v>
       </c>
       <c r="L48" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-97</v>
       </c>
       <c r="M48" s="1"/>
@@ -6116,14 +6246,14 @@
       </c>
       <c r="Q48" s="1"/>
       <c r="R48" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>53</v>
       </c>
       <c r="S48" s="5">
         <v>200</v>
       </c>
       <c r="T48" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>140</v>
       </c>
       <c r="U48" s="1">
@@ -6131,7 +6261,7 @@
         <v>2.6603773584905661</v>
       </c>
       <c r="V48" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1.8867924528301886E-2</v>
       </c>
       <c r="W48" s="1">
@@ -6169,7 +6299,10 @@
         <f t="shared" si="7"/>
         <v>49</v>
       </c>
-      <c r="AI48" s="1"/>
+      <c r="AI48" s="1">
+        <f t="shared" si="8"/>
+        <v>18.549999999999997</v>
+      </c>
       <c r="AJ48" s="1"/>
       <c r="AK48" s="1"/>
       <c r="AL48" s="1"/>
@@ -6215,7 +6348,7 @@
         <v>322</v>
       </c>
       <c r="L49" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-36</v>
       </c>
       <c r="M49" s="1"/>
@@ -6226,14 +6359,14 @@
       <c r="P49" s="1"/>
       <c r="Q49" s="1"/>
       <c r="R49" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>57.2</v>
       </c>
       <c r="S49" s="5">
         <v>250</v>
       </c>
       <c r="T49" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>175</v>
       </c>
       <c r="U49" s="1">
@@ -6241,7 +6374,7 @@
         <v>5.1311188811188808</v>
       </c>
       <c r="V49" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2.0716783216783217</v>
       </c>
       <c r="W49" s="1">
@@ -6279,7 +6412,10 @@
         <f t="shared" si="7"/>
         <v>70</v>
       </c>
-      <c r="AI49" s="1"/>
+      <c r="AI49" s="1">
+        <f t="shared" si="8"/>
+        <v>22.880000000000003</v>
+      </c>
       <c r="AJ49" s="1"/>
       <c r="AK49" s="1"/>
       <c r="AL49" s="1"/>
@@ -6325,7 +6461,7 @@
         <v>74.7</v>
       </c>
       <c r="L50" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>6.2929999999999922</v>
       </c>
       <c r="M50" s="1"/>
@@ -6336,7 +6472,7 @@
       <c r="P50" s="1"/>
       <c r="Q50" s="1"/>
       <c r="R50" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>16.198599999999999</v>
       </c>
       <c r="S50" s="5">
@@ -6344,7 +6480,7 @@
         <v>75.913799999999995</v>
       </c>
       <c r="T50" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>75.913799999999995</v>
       </c>
       <c r="U50" s="1">
@@ -6352,7 +6488,7 @@
         <v>8</v>
       </c>
       <c r="V50" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>3.3135579617991677</v>
       </c>
       <c r="W50" s="1">
@@ -6390,7 +6526,10 @@
         <f t="shared" si="7"/>
         <v>76</v>
       </c>
-      <c r="AI50" s="1"/>
+      <c r="AI50" s="1">
+        <f t="shared" si="8"/>
+        <v>16.198599999999999</v>
+      </c>
       <c r="AJ50" s="1"/>
       <c r="AK50" s="1"/>
       <c r="AL50" s="1"/>
@@ -6436,7 +6575,7 @@
         <v>136.1</v>
       </c>
       <c r="L51" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>6.171999999999997</v>
       </c>
       <c r="M51" s="1"/>
@@ -6447,15 +6586,15 @@
       <c r="P51" s="1"/>
       <c r="Q51" s="1"/>
       <c r="R51" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>28.4544</v>
       </c>
       <c r="S51" s="5">
-        <f t="shared" ref="S51:S61" si="18">11*R51-Q51-P51-O51-F51</f>
+        <f t="shared" ref="S51:S61" si="19">11*R51-Q51-P51-O51-F51</f>
         <v>183.20839999999998</v>
       </c>
       <c r="T51" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>183.20839999999998</v>
       </c>
       <c r="U51" s="1">
@@ -6463,7 +6602,7 @@
         <v>11</v>
       </c>
       <c r="V51" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>4.5613332208726955</v>
       </c>
       <c r="W51" s="1">
@@ -6501,7 +6640,10 @@
         <f t="shared" si="7"/>
         <v>183</v>
       </c>
-      <c r="AI51" s="1"/>
+      <c r="AI51" s="1">
+        <f t="shared" si="8"/>
+        <v>28.4544</v>
+      </c>
       <c r="AJ51" s="1"/>
       <c r="AK51" s="1"/>
       <c r="AL51" s="1"/>
@@ -6543,7 +6685,7 @@
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-0.15</v>
       </c>
       <c r="M52" s="1"/>
@@ -6556,14 +6698,14 @@
       </c>
       <c r="Q52" s="1"/>
       <c r="R52" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-0.03</v>
       </c>
       <c r="S52" s="5">
         <v>50</v>
       </c>
       <c r="T52" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>50</v>
       </c>
       <c r="U52" s="1">
@@ -6571,7 +6713,7 @@
         <v>-1662.5</v>
       </c>
       <c r="V52" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>4.166666666666667</v>
       </c>
       <c r="W52" s="1">
@@ -6609,7 +6751,10 @@
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="AI52" s="1"/>
+      <c r="AI52" s="1">
+        <f t="shared" si="8"/>
+        <v>-0.03</v>
+      </c>
       <c r="AJ52" s="1"/>
       <c r="AK52" s="1"/>
       <c r="AL52" s="1"/>
@@ -6655,7 +6800,7 @@
         <v>108</v>
       </c>
       <c r="L53" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-7</v>
       </c>
       <c r="M53" s="1"/>
@@ -6666,15 +6811,15 @@
       <c r="P53" s="1"/>
       <c r="Q53" s="1"/>
       <c r="R53" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>20.2</v>
       </c>
       <c r="S53" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>75.937999999999931</v>
       </c>
       <c r="T53" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>75.937999999999931</v>
       </c>
       <c r="U53" s="1">
@@ -6682,7 +6827,7 @@
         <v>11</v>
       </c>
       <c r="V53" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>7.2406930693069338</v>
       </c>
       <c r="W53" s="1">
@@ -6720,7 +6865,10 @@
         <f t="shared" si="7"/>
         <v>34</v>
       </c>
-      <c r="AI53" s="1"/>
+      <c r="AI53" s="1">
+        <f t="shared" si="8"/>
+        <v>9.09</v>
+      </c>
       <c r="AJ53" s="1"/>
       <c r="AK53" s="1"/>
       <c r="AL53" s="1"/>
@@ -6766,7 +6914,7 @@
         <v>250</v>
       </c>
       <c r="L54" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-9</v>
       </c>
       <c r="M54" s="1"/>
@@ -6777,15 +6925,15 @@
       <c r="P54" s="1"/>
       <c r="Q54" s="1"/>
       <c r="R54" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>48.2</v>
       </c>
       <c r="S54" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>213.73400000000004</v>
       </c>
       <c r="T54" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>213.73400000000004</v>
       </c>
       <c r="U54" s="1">
@@ -6793,7 +6941,7 @@
         <v>11</v>
       </c>
       <c r="V54" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>6.5656846473029047</v>
       </c>
       <c r="W54" s="1">
@@ -6831,7 +6979,10 @@
         <f t="shared" si="7"/>
         <v>96</v>
       </c>
-      <c r="AI54" s="1"/>
+      <c r="AI54" s="1">
+        <f t="shared" si="8"/>
+        <v>21.69</v>
+      </c>
       <c r="AJ54" s="1"/>
       <c r="AK54" s="1"/>
       <c r="AL54" s="1"/>
@@ -6875,7 +7026,7 @@
         <v>170</v>
       </c>
       <c r="L55" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-10</v>
       </c>
       <c r="M55" s="1"/>
@@ -6888,14 +7039,14 @@
       </c>
       <c r="Q55" s="1"/>
       <c r="R55" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>32</v>
       </c>
       <c r="S55" s="5">
         <v>100</v>
       </c>
       <c r="T55" s="5">
-        <f t="shared" ref="T55:T56" si="19">S55*0.7</f>
+        <f t="shared" ref="T55:T56" si="20">S55*0.7</f>
         <v>70</v>
       </c>
       <c r="U55" s="1">
@@ -6903,7 +7054,7 @@
         <v>2.09375</v>
       </c>
       <c r="V55" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-9.3749999999999778E-2</v>
       </c>
       <c r="W55" s="1">
@@ -6941,7 +7092,10 @@
         <f t="shared" si="7"/>
         <v>28</v>
       </c>
-      <c r="AI55" s="1"/>
+      <c r="AI55" s="1">
+        <f t="shared" si="8"/>
+        <v>12.8</v>
+      </c>
       <c r="AJ55" s="1"/>
       <c r="AK55" s="1"/>
       <c r="AL55" s="1"/>
@@ -6987,7 +7141,7 @@
         <v>190</v>
       </c>
       <c r="L56" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-14</v>
       </c>
       <c r="M56" s="1"/>
@@ -6998,14 +7152,14 @@
       <c r="P56" s="1"/>
       <c r="Q56" s="1"/>
       <c r="R56" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>35.200000000000003</v>
       </c>
       <c r="S56" s="5">
         <v>150</v>
       </c>
       <c r="T56" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>105</v>
       </c>
       <c r="U56" s="1">
@@ -7013,7 +7167,7 @@
         <v>6.2215909090909083</v>
       </c>
       <c r="V56" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>3.2386363636363633</v>
       </c>
       <c r="W56" s="1">
@@ -7051,7 +7205,10 @@
         <f t="shared" si="7"/>
         <v>42</v>
       </c>
-      <c r="AI56" s="1"/>
+      <c r="AI56" s="1">
+        <f t="shared" si="8"/>
+        <v>14.080000000000002</v>
+      </c>
       <c r="AJ56" s="1"/>
       <c r="AK56" s="1"/>
       <c r="AL56" s="1"/>
@@ -7097,7 +7254,7 @@
         <v>125.15</v>
       </c>
       <c r="L57" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1.9169999999999874</v>
       </c>
       <c r="M57" s="1"/>
@@ -7108,15 +7265,15 @@
       <c r="P57" s="1"/>
       <c r="Q57" s="1"/>
       <c r="R57" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>25.413399999999999</v>
       </c>
       <c r="S57" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>158.22423399999997</v>
       </c>
       <c r="T57" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>158.22423399999997</v>
       </c>
       <c r="U57" s="1">
@@ -7124,7 +7281,7 @@
         <v>11</v>
       </c>
       <c r="V57" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>4.773984039915951</v>
       </c>
       <c r="W57" s="1">
@@ -7162,7 +7319,10 @@
         <f t="shared" si="7"/>
         <v>158</v>
       </c>
-      <c r="AI57" s="1"/>
+      <c r="AI57" s="1">
+        <f t="shared" si="8"/>
+        <v>25.413399999999999</v>
+      </c>
       <c r="AJ57" s="1"/>
       <c r="AK57" s="1"/>
       <c r="AL57" s="1"/>
@@ -7206,7 +7366,7 @@
         <v>225</v>
       </c>
       <c r="L58" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-1</v>
       </c>
       <c r="M58" s="1"/>
@@ -7217,15 +7377,15 @@
       <c r="P58" s="1"/>
       <c r="Q58" s="1"/>
       <c r="R58" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>44.8</v>
       </c>
       <c r="S58" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>274</v>
       </c>
       <c r="T58" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>274</v>
       </c>
       <c r="U58" s="1">
@@ -7233,7 +7393,7 @@
         <v>11</v>
       </c>
       <c r="V58" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>4.8839285714285703</v>
       </c>
       <c r="W58" s="1">
@@ -7271,7 +7431,10 @@
         <f t="shared" si="7"/>
         <v>27</v>
       </c>
-      <c r="AI58" s="1"/>
+      <c r="AI58" s="1">
+        <f t="shared" si="8"/>
+        <v>4.4799999999999995</v>
+      </c>
       <c r="AJ58" s="1"/>
       <c r="AK58" s="1"/>
       <c r="AL58" s="1"/>
@@ -7317,7 +7480,7 @@
         <v>92.6</v>
       </c>
       <c r="L59" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-15.072999999999993</v>
       </c>
       <c r="M59" s="1"/>
@@ -7328,15 +7491,15 @@
       <c r="P59" s="1"/>
       <c r="Q59" s="1"/>
       <c r="R59" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>15.5054</v>
       </c>
       <c r="S59" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>93.523400000000009</v>
       </c>
       <c r="T59" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>93.523400000000009</v>
       </c>
       <c r="U59" s="1">
@@ -7344,7 +7507,7 @@
         <v>11</v>
       </c>
       <c r="V59" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>4.9683336128058615</v>
       </c>
       <c r="W59" s="1">
@@ -7382,7 +7545,10 @@
         <f t="shared" si="7"/>
         <v>94</v>
       </c>
-      <c r="AI59" s="1"/>
+      <c r="AI59" s="1">
+        <f t="shared" si="8"/>
+        <v>15.5054</v>
+      </c>
       <c r="AJ59" s="1"/>
       <c r="AK59" s="1"/>
       <c r="AL59" s="1"/>
@@ -7428,7 +7594,7 @@
         <v>35.5</v>
       </c>
       <c r="L60" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4.4129999999999967</v>
       </c>
       <c r="M60" s="1"/>
@@ -7439,7 +7605,7 @@
       <c r="P60" s="1"/>
       <c r="Q60" s="1"/>
       <c r="R60" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>7.9825999999999997</v>
       </c>
       <c r="S60" s="5">
@@ -7447,7 +7613,7 @@
         <v>44.672400000000003</v>
       </c>
       <c r="T60" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>44.672400000000003</v>
       </c>
       <c r="U60" s="1">
@@ -7455,7 +7621,7 @@
         <v>9</v>
       </c>
       <c r="V60" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>3.4037782176233309</v>
       </c>
       <c r="W60" s="1">
@@ -7493,7 +7659,10 @@
         <f t="shared" si="7"/>
         <v>45</v>
       </c>
-      <c r="AI60" s="1"/>
+      <c r="AI60" s="1">
+        <f t="shared" si="8"/>
+        <v>7.9825999999999997</v>
+      </c>
       <c r="AJ60" s="1"/>
       <c r="AK60" s="1"/>
       <c r="AL60" s="1"/>
@@ -7537,7 +7706,7 @@
         <v>240</v>
       </c>
       <c r="L61" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>126</v>
       </c>
       <c r="M61" s="1"/>
@@ -7548,15 +7717,15 @@
       <c r="P61" s="1"/>
       <c r="Q61" s="1"/>
       <c r="R61" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>73.2</v>
       </c>
       <c r="S61" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>465.56600000000003</v>
       </c>
       <c r="T61" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>465.56600000000003</v>
       </c>
       <c r="U61" s="1">
@@ -7564,7 +7733,7 @@
         <v>11</v>
       </c>
       <c r="V61" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>4.6398087431693993</v>
       </c>
       <c r="W61" s="1">
@@ -7602,7 +7771,10 @@
         <f t="shared" si="7"/>
         <v>47</v>
       </c>
-      <c r="AI61" s="1"/>
+      <c r="AI61" s="1">
+        <f t="shared" si="8"/>
+        <v>7.32</v>
+      </c>
       <c r="AJ61" s="1"/>
       <c r="AK61" s="1"/>
       <c r="AL61" s="1"/>
@@ -7646,7 +7818,7 @@
         <v>45</v>
       </c>
       <c r="L62" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-1</v>
       </c>
       <c r="M62" s="1"/>
@@ -7657,7 +7829,7 @@
       <c r="P62" s="1"/>
       <c r="Q62" s="1"/>
       <c r="R62" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="S62" s="5">
@@ -7665,7 +7837,7 @@
         <v>49.2</v>
       </c>
       <c r="T62" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>49.2</v>
       </c>
       <c r="U62" s="1">
@@ -7673,7 +7845,7 @@
         <v>9</v>
       </c>
       <c r="V62" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>3.4090909090909087</v>
       </c>
       <c r="W62" s="1">
@@ -7711,7 +7883,10 @@
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
-      <c r="AI62" s="1"/>
+      <c r="AI62" s="1">
+        <f t="shared" si="8"/>
+        <v>3.5200000000000005</v>
+      </c>
       <c r="AJ62" s="1"/>
       <c r="AK62" s="1"/>
       <c r="AL62" s="1"/>
@@ -7757,7 +7932,7 @@
         <v>98.8</v>
       </c>
       <c r="L63" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-23.018000000000001</v>
       </c>
       <c r="M63" s="1"/>
@@ -7768,7 +7943,7 @@
       <c r="P63" s="1"/>
       <c r="Q63" s="1"/>
       <c r="R63" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>15.1564</v>
       </c>
       <c r="S63" s="5">
@@ -7783,7 +7958,7 @@
         <v>5.9723945000131957</v>
       </c>
       <c r="V63" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1.8157346071626508</v>
       </c>
       <c r="W63" s="1">
@@ -7823,7 +7998,10 @@
         <f t="shared" si="7"/>
         <v>63</v>
       </c>
-      <c r="AI63" s="1"/>
+      <c r="AI63" s="1">
+        <f t="shared" si="8"/>
+        <v>15.1564</v>
+      </c>
       <c r="AJ63" s="1"/>
       <c r="AK63" s="1"/>
       <c r="AL63" s="1"/>
@@ -7869,7 +8047,7 @@
         <v>195.4</v>
       </c>
       <c r="L64" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-21.180000000000007</v>
       </c>
       <c r="M64" s="1"/>
@@ -7880,7 +8058,7 @@
       <c r="P64" s="1"/>
       <c r="Q64" s="1"/>
       <c r="R64" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>34.844000000000001</v>
       </c>
       <c r="S64" s="5">
@@ -7888,7 +8066,7 @@
         <v>221.47503799999998</v>
       </c>
       <c r="T64" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>221.47503799999998</v>
       </c>
       <c r="U64" s="1">
@@ -7896,7 +8074,7 @@
         <v>10</v>
       </c>
       <c r="V64" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>3.6438113305016646</v>
       </c>
       <c r="W64" s="1">
@@ -7936,7 +8114,10 @@
         <f t="shared" si="7"/>
         <v>221</v>
       </c>
-      <c r="AI64" s="1"/>
+      <c r="AI64" s="1">
+        <f t="shared" si="8"/>
+        <v>34.844000000000001</v>
+      </c>
       <c r="AJ64" s="1"/>
       <c r="AK64" s="1"/>
       <c r="AL64" s="1"/>
@@ -7982,7 +8163,7 @@
         <v>564</v>
       </c>
       <c r="L65" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-319</v>
       </c>
       <c r="M65" s="1"/>
@@ -7993,12 +8174,12 @@
       <c r="P65" s="1"/>
       <c r="Q65" s="1"/>
       <c r="R65" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>49</v>
       </c>
       <c r="S65" s="5"/>
       <c r="T65" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U65" s="1">
@@ -8006,7 +8187,7 @@
         <v>11.646122448979591</v>
       </c>
       <c r="V65" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>11.646122448979591</v>
       </c>
       <c r="W65" s="1">
@@ -8044,7 +8225,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AI65" s="1"/>
+      <c r="AI65" s="1">
+        <f t="shared" si="8"/>
+        <v>19.600000000000001</v>
+      </c>
       <c r="AJ65" s="1"/>
       <c r="AK65" s="1"/>
       <c r="AL65" s="1"/>
@@ -8090,7 +8274,7 @@
         <v>474</v>
       </c>
       <c r="L66" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-2</v>
       </c>
       <c r="M66" s="1"/>
@@ -8101,14 +8285,14 @@
       <c r="P66" s="1"/>
       <c r="Q66" s="1"/>
       <c r="R66" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>94.4</v>
       </c>
       <c r="S66" s="5">
         <v>400</v>
       </c>
       <c r="T66" s="5">
-        <f t="shared" ref="T66:T70" si="20">S66*0.7</f>
+        <f t="shared" ref="T66:T70" si="21">S66*0.7</f>
         <v>280</v>
       </c>
       <c r="U66" s="1">
@@ -8116,7 +8300,7 @@
         <v>4.3326271186440675</v>
       </c>
       <c r="V66" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1.3665254237288136</v>
       </c>
       <c r="W66" s="1">
@@ -8154,7 +8338,10 @@
         <f t="shared" si="7"/>
         <v>112</v>
       </c>
-      <c r="AI66" s="1"/>
+      <c r="AI66" s="1">
+        <f t="shared" si="8"/>
+        <v>37.760000000000005</v>
+      </c>
       <c r="AJ66" s="1"/>
       <c r="AK66" s="1"/>
       <c r="AL66" s="1"/>
@@ -8200,7 +8387,7 @@
         <v>167</v>
       </c>
       <c r="L67" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-6.4310000000000116</v>
       </c>
       <c r="M67" s="1"/>
@@ -8213,14 +8400,14 @@
       </c>
       <c r="Q67" s="1"/>
       <c r="R67" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>32.113799999999998</v>
       </c>
       <c r="S67" s="5">
         <v>100</v>
       </c>
       <c r="T67" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>70</v>
       </c>
       <c r="U67" s="1">
@@ -8228,7 +8415,7 @@
         <v>1.9363638062141515</v>
       </c>
       <c r="V67" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-0.24338446399990002</v>
       </c>
       <c r="W67" s="1">
@@ -8266,7 +8453,10 @@
         <f t="shared" si="7"/>
         <v>70</v>
       </c>
-      <c r="AI67" s="1"/>
+      <c r="AI67" s="1">
+        <f t="shared" si="8"/>
+        <v>32.113799999999998</v>
+      </c>
       <c r="AJ67" s="1"/>
       <c r="AK67" s="1"/>
       <c r="AL67" s="1"/>
@@ -8312,7 +8502,7 @@
         <v>108.5</v>
       </c>
       <c r="L68" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-40.631</v>
       </c>
       <c r="M68" s="1"/>
@@ -8325,14 +8515,14 @@
       </c>
       <c r="Q68" s="1"/>
       <c r="R68" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>13.5738</v>
       </c>
       <c r="S68" s="5">
         <v>100</v>
       </c>
       <c r="T68" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>70</v>
       </c>
       <c r="U68" s="1">
@@ -8340,7 +8530,7 @@
         <v>4.908942226937187</v>
       </c>
       <c r="V68" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-0.24805139312499111</v>
       </c>
       <c r="W68" s="1">
@@ -8378,7 +8568,10 @@
         <f t="shared" si="7"/>
         <v>70</v>
       </c>
-      <c r="AI68" s="1"/>
+      <c r="AI68" s="1">
+        <f t="shared" si="8"/>
+        <v>13.5738</v>
+      </c>
       <c r="AJ68" s="1"/>
       <c r="AK68" s="1"/>
       <c r="AL68" s="1"/>
@@ -8424,7 +8617,7 @@
         <v>334.5</v>
       </c>
       <c r="L69" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>14.589999999999975</v>
       </c>
       <c r="M69" s="1"/>
@@ -8437,14 +8630,14 @@
       </c>
       <c r="Q69" s="1"/>
       <c r="R69" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>69.817999999999998</v>
       </c>
       <c r="S69" s="5">
         <v>200</v>
       </c>
       <c r="T69" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>140</v>
       </c>
       <c r="U69" s="1">
@@ -8452,7 +8645,7 @@
         <v>1.9855902489329413</v>
       </c>
       <c r="V69" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-1.9623306310692229E-2</v>
       </c>
       <c r="W69" s="1">
@@ -8490,7 +8683,10 @@
         <f t="shared" si="7"/>
         <v>140</v>
       </c>
-      <c r="AI69" s="1"/>
+      <c r="AI69" s="1">
+        <f t="shared" si="8"/>
+        <v>69.817999999999998</v>
+      </c>
       <c r="AJ69" s="1"/>
       <c r="AK69" s="1"/>
       <c r="AL69" s="1"/>
@@ -8536,7 +8732,7 @@
         <v>171.8</v>
       </c>
       <c r="L70" s="1">
-        <f t="shared" ref="L70:L101" si="21">E70-K70</f>
+        <f t="shared" ref="L70:L101" si="22">E70-K70</f>
         <v>-16.400000000000006</v>
       </c>
       <c r="M70" s="1"/>
@@ -8549,14 +8745,14 @@
       </c>
       <c r="Q70" s="1"/>
       <c r="R70" s="1">
-        <f t="shared" ref="R70:R101" si="22">E70/5</f>
+        <f t="shared" ref="R70:R101" si="23">E70/5</f>
         <v>31.080000000000002</v>
       </c>
       <c r="S70" s="5">
         <v>100</v>
       </c>
       <c r="T70" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>70</v>
       </c>
       <c r="U70" s="1">
@@ -8564,7 +8760,7 @@
         <v>2.607381531531531</v>
       </c>
       <c r="V70" s="1">
-        <f t="shared" ref="V70:V101" si="23">(F70+O70+P70+Q70)/R70</f>
+        <f t="shared" ref="V70:V101" si="24">(F70+O70+P70+Q70)/R70</f>
         <v>0.3551292792792789</v>
       </c>
       <c r="W70" s="1">
@@ -8602,7 +8798,10 @@
         <f t="shared" si="7"/>
         <v>70</v>
       </c>
-      <c r="AI70" s="1"/>
+      <c r="AI70" s="1">
+        <f t="shared" si="8"/>
+        <v>31.080000000000002</v>
+      </c>
       <c r="AJ70" s="1"/>
       <c r="AK70" s="1"/>
       <c r="AL70" s="1"/>
@@ -8646,7 +8845,7 @@
         <v>16</v>
       </c>
       <c r="L71" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-2</v>
       </c>
       <c r="M71" s="1"/>
@@ -8657,20 +8856,20 @@
       <c r="P71" s="1"/>
       <c r="Q71" s="1"/>
       <c r="R71" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>2.8</v>
       </c>
       <c r="S71" s="5"/>
       <c r="T71" s="5">
-        <f t="shared" ref="T71:T133" si="24">S71</f>
+        <f t="shared" ref="T71:T133" si="25">S71</f>
         <v>0</v>
       </c>
       <c r="U71" s="1">
-        <f t="shared" ref="U71:U133" si="25">(F71+O71+P71+Q71+T71)/R71</f>
+        <f t="shared" ref="U71:U133" si="26">(F71+O71+P71+Q71+T71)/R71</f>
         <v>11.428571428571429</v>
       </c>
       <c r="V71" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>11.428571428571429</v>
       </c>
       <c r="W71" s="1">
@@ -8705,10 +8904,13 @@
       </c>
       <c r="AG71" s="1"/>
       <c r="AH71" s="1">
-        <f t="shared" ref="AH71:AH133" si="26">ROUND(G71*T71,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AI71" s="1"/>
+        <f t="shared" ref="AH71:AH133" si="27">ROUND(G71*T71,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI71" s="1">
+        <f t="shared" ref="AI71:AI133" si="28">R71*G71</f>
+        <v>1.68</v>
+      </c>
       <c r="AJ71" s="1"/>
       <c r="AK71" s="1"/>
       <c r="AL71" s="1"/>
@@ -8754,7 +8956,7 @@
         <v>480.5</v>
       </c>
       <c r="L72" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-36.634000000000015</v>
       </c>
       <c r="M72" s="1"/>
@@ -8765,7 +8967,7 @@
       <c r="P72" s="1"/>
       <c r="Q72" s="1"/>
       <c r="R72" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>88.773200000000003</v>
       </c>
       <c r="S72" s="5">
@@ -8777,11 +8979,11 @@
         <v>476.84236000000004</v>
       </c>
       <c r="U72" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>7.3000000000000007</v>
       </c>
       <c r="V72" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1.9285324850292656</v>
       </c>
       <c r="W72" s="1">
@@ -8816,10 +9018,13 @@
       </c>
       <c r="AG72" s="1"/>
       <c r="AH72" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>477</v>
       </c>
-      <c r="AI72" s="1"/>
+      <c r="AI72" s="1">
+        <f t="shared" si="28"/>
+        <v>88.773200000000003</v>
+      </c>
       <c r="AJ72" s="1"/>
       <c r="AK72" s="1"/>
       <c r="AL72" s="1"/>
@@ -8853,7 +9058,7 @@
       <c r="J73" s="9"/>
       <c r="K73" s="9"/>
       <c r="L73" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M73" s="9"/>
@@ -8864,20 +9069,20 @@
       <c r="P73" s="9"/>
       <c r="Q73" s="9"/>
       <c r="R73" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="S73" s="11"/>
       <c r="T73" s="5">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="U73" s="1" t="e">
+        <f t="shared" si="26"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V73" s="9" t="e">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="U73" s="1" t="e">
-        <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V73" s="9" t="e">
-        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W73" s="9">
@@ -8914,10 +9119,13 @@
         <v>47</v>
       </c>
       <c r="AH73" s="1">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AI73" s="1"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AI73" s="1">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AJ73" s="1"/>
       <c r="AK73" s="1"/>
       <c r="AL73" s="1"/>
@@ -8963,7 +9171,7 @@
         <v>103</v>
       </c>
       <c r="L74" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>9</v>
       </c>
       <c r="M74" s="1"/>
@@ -8974,23 +9182,23 @@
       <c r="P74" s="1"/>
       <c r="Q74" s="1"/>
       <c r="R74" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>22.4</v>
       </c>
       <c r="S74" s="5">
-        <f t="shared" ref="S74:S78" si="27">11*R74-Q74-P74-O74-F74</f>
+        <f t="shared" ref="S74:S78" si="29">11*R74-Q74-P74-O74-F74</f>
         <v>87.951999999999984</v>
       </c>
       <c r="T74" s="5">
+        <f t="shared" si="25"/>
+        <v>87.951999999999984</v>
+      </c>
+      <c r="U74" s="1">
+        <f t="shared" si="26"/>
+        <v>11</v>
+      </c>
+      <c r="V74" s="1">
         <f t="shared" si="24"/>
-        <v>87.951999999999984</v>
-      </c>
-      <c r="U74" s="1">
-        <f t="shared" si="25"/>
-        <v>11</v>
-      </c>
-      <c r="V74" s="1">
-        <f t="shared" si="23"/>
         <v>7.0735714285714284</v>
       </c>
       <c r="W74" s="1">
@@ -9025,10 +9233,13 @@
       </c>
       <c r="AG74" s="1"/>
       <c r="AH74" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>53</v>
       </c>
-      <c r="AI74" s="1"/>
+      <c r="AI74" s="1">
+        <f t="shared" si="28"/>
+        <v>13.44</v>
+      </c>
       <c r="AJ74" s="1"/>
       <c r="AK74" s="1"/>
       <c r="AL74" s="1"/>
@@ -9074,7 +9285,7 @@
         <v>97</v>
       </c>
       <c r="L75" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-2</v>
       </c>
       <c r="M75" s="1"/>
@@ -9085,23 +9296,23 @@
       <c r="P75" s="1"/>
       <c r="Q75" s="1"/>
       <c r="R75" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>19</v>
       </c>
       <c r="S75" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>81.247999999999962</v>
       </c>
       <c r="T75" s="5">
+        <f t="shared" si="25"/>
+        <v>81.247999999999962</v>
+      </c>
+      <c r="U75" s="1">
+        <f t="shared" si="26"/>
+        <v>11</v>
+      </c>
+      <c r="V75" s="1">
         <f t="shared" si="24"/>
-        <v>81.247999999999962</v>
-      </c>
-      <c r="U75" s="1">
-        <f t="shared" si="25"/>
-        <v>11</v>
-      </c>
-      <c r="V75" s="1">
-        <f t="shared" si="23"/>
         <v>6.7237894736842128</v>
       </c>
       <c r="W75" s="1">
@@ -9136,10 +9347,13 @@
       </c>
       <c r="AG75" s="1"/>
       <c r="AH75" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>32</v>
       </c>
-      <c r="AI75" s="1"/>
+      <c r="AI75" s="1">
+        <f t="shared" si="28"/>
+        <v>7.6000000000000005</v>
+      </c>
       <c r="AJ75" s="1"/>
       <c r="AK75" s="1"/>
       <c r="AL75" s="1"/>
@@ -9185,7 +9399,7 @@
         <v>195</v>
       </c>
       <c r="L76" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-7</v>
       </c>
       <c r="M76" s="1"/>
@@ -9196,23 +9410,23 @@
       <c r="P76" s="1"/>
       <c r="Q76" s="1"/>
       <c r="R76" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>37.6</v>
       </c>
       <c r="S76" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>148.98799999999991</v>
       </c>
       <c r="T76" s="5">
+        <f t="shared" si="25"/>
+        <v>148.98799999999991</v>
+      </c>
+      <c r="U76" s="1">
+        <f t="shared" si="26"/>
+        <v>11</v>
+      </c>
+      <c r="V76" s="1">
         <f t="shared" si="24"/>
-        <v>148.98799999999991</v>
-      </c>
-      <c r="U76" s="1">
-        <f t="shared" si="25"/>
-        <v>11</v>
-      </c>
-      <c r="V76" s="1">
-        <f t="shared" si="23"/>
         <v>7.0375531914893639</v>
       </c>
       <c r="W76" s="1">
@@ -9247,10 +9461,13 @@
       </c>
       <c r="AG76" s="1"/>
       <c r="AH76" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>49</v>
       </c>
-      <c r="AI76" s="1"/>
+      <c r="AI76" s="1">
+        <f t="shared" si="28"/>
+        <v>12.408000000000001</v>
+      </c>
       <c r="AJ76" s="1"/>
       <c r="AK76" s="1"/>
       <c r="AL76" s="1"/>
@@ -9296,7 +9513,7 @@
         <v>79</v>
       </c>
       <c r="L77" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-40</v>
       </c>
       <c r="M77" s="1"/>
@@ -9307,20 +9524,20 @@
       <c r="P77" s="1"/>
       <c r="Q77" s="1"/>
       <c r="R77" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>7.8</v>
       </c>
       <c r="S77" s="5"/>
       <c r="T77" s="5">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="U77" s="1">
+        <f t="shared" si="26"/>
+        <v>19.970256410256411</v>
+      </c>
+      <c r="V77" s="1">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="U77" s="1">
-        <f t="shared" si="25"/>
-        <v>19.970256410256411</v>
-      </c>
-      <c r="V77" s="1">
-        <f t="shared" si="23"/>
         <v>19.970256410256411</v>
       </c>
       <c r="W77" s="1">
@@ -9355,10 +9572,13 @@
       </c>
       <c r="AG77" s="1"/>
       <c r="AH77" s="1">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AI77" s="1"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AI77" s="1">
+        <f t="shared" si="28"/>
+        <v>2.73</v>
+      </c>
       <c r="AJ77" s="1"/>
       <c r="AK77" s="1"/>
       <c r="AL77" s="1"/>
@@ -9404,7 +9624,7 @@
         <v>221</v>
       </c>
       <c r="L78" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-2</v>
       </c>
       <c r="M78" s="1"/>
@@ -9415,23 +9635,23 @@
       <c r="P78" s="1"/>
       <c r="Q78" s="1"/>
       <c r="R78" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>43.8</v>
       </c>
       <c r="S78" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>229.41200000000006</v>
       </c>
       <c r="T78" s="5">
+        <f t="shared" si="25"/>
+        <v>229.41200000000006</v>
+      </c>
+      <c r="U78" s="1">
+        <f t="shared" si="26"/>
+        <v>11</v>
+      </c>
+      <c r="V78" s="1">
         <f t="shared" si="24"/>
-        <v>229.41200000000006</v>
-      </c>
-      <c r="U78" s="1">
-        <f t="shared" si="25"/>
-        <v>11</v>
-      </c>
-      <c r="V78" s="1">
-        <f t="shared" si="23"/>
         <v>5.7622831050228287</v>
       </c>
       <c r="W78" s="1">
@@ -9466,10 +9686,13 @@
       </c>
       <c r="AG78" s="1"/>
       <c r="AH78" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>85</v>
       </c>
-      <c r="AI78" s="1"/>
+      <c r="AI78" s="1">
+        <f t="shared" si="28"/>
+        <v>16.206</v>
+      </c>
       <c r="AJ78" s="1"/>
       <c r="AK78" s="1"/>
       <c r="AL78" s="1"/>
@@ -9503,7 +9726,7 @@
       <c r="J79" s="9"/>
       <c r="K79" s="9"/>
       <c r="L79" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M79" s="9"/>
@@ -9514,20 +9737,20 @@
       <c r="P79" s="9"/>
       <c r="Q79" s="9"/>
       <c r="R79" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="S79" s="11"/>
       <c r="T79" s="5">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="U79" s="1" t="e">
+        <f t="shared" si="26"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V79" s="9" t="e">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="U79" s="1" t="e">
-        <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V79" s="9" t="e">
-        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W79" s="9">
@@ -9564,10 +9787,13 @@
         <v>47</v>
       </c>
       <c r="AH79" s="1">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AI79" s="1"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AI79" s="1">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AJ79" s="1"/>
       <c r="AK79" s="1"/>
       <c r="AL79" s="1"/>
@@ -9613,7 +9839,7 @@
         <v>92</v>
       </c>
       <c r="L80" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-9</v>
       </c>
       <c r="M80" s="1"/>
@@ -9624,23 +9850,23 @@
       <c r="P80" s="1"/>
       <c r="Q80" s="1"/>
       <c r="R80" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>16.600000000000001</v>
       </c>
       <c r="S80" s="5">
-        <f t="shared" ref="S80" si="28">11*R80-Q80-P80-O80-F80</f>
+        <f t="shared" ref="S80" si="30">11*R80-Q80-P80-O80-F80</f>
         <v>91.742000000000019</v>
       </c>
       <c r="T80" s="5">
+        <f t="shared" si="25"/>
+        <v>91.742000000000019</v>
+      </c>
+      <c r="U80" s="1">
+        <f t="shared" si="26"/>
+        <v>11</v>
+      </c>
+      <c r="V80" s="1">
         <f t="shared" si="24"/>
-        <v>91.742000000000019</v>
-      </c>
-      <c r="U80" s="1">
-        <f t="shared" si="25"/>
-        <v>11</v>
-      </c>
-      <c r="V80" s="1">
-        <f t="shared" si="23"/>
         <v>5.4733734939759033</v>
       </c>
       <c r="W80" s="1">
@@ -9675,10 +9901,13 @@
       </c>
       <c r="AG80" s="1"/>
       <c r="AH80" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>30</v>
       </c>
-      <c r="AI80" s="1"/>
+      <c r="AI80" s="1">
+        <f t="shared" si="28"/>
+        <v>5.4780000000000006</v>
+      </c>
       <c r="AJ80" s="1"/>
       <c r="AK80" s="1"/>
       <c r="AL80" s="1"/>
@@ -9724,7 +9953,7 @@
         <v>77</v>
       </c>
       <c r="L81" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-3</v>
       </c>
       <c r="M81" s="1"/>
@@ -9735,20 +9964,20 @@
       <c r="P81" s="1"/>
       <c r="Q81" s="1"/>
       <c r="R81" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>14.8</v>
       </c>
       <c r="S81" s="5"/>
       <c r="T81" s="5">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="U81" s="1">
+        <f t="shared" si="26"/>
+        <v>15.810810810810811</v>
+      </c>
+      <c r="V81" s="1">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="U81" s="1">
-        <f t="shared" si="25"/>
-        <v>15.810810810810811</v>
-      </c>
-      <c r="V81" s="1">
-        <f t="shared" si="23"/>
         <v>15.810810810810811</v>
       </c>
       <c r="W81" s="1">
@@ -9785,10 +10014,13 @@
         <v>88</v>
       </c>
       <c r="AH81" s="1">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AI81" s="1"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AI81" s="1">
+        <f t="shared" si="28"/>
+        <v>5.9200000000000008</v>
+      </c>
       <c r="AJ81" s="1"/>
       <c r="AK81" s="1"/>
       <c r="AL81" s="1"/>
@@ -9832,7 +10064,7 @@
         <v>25</v>
       </c>
       <c r="L82" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-15</v>
       </c>
       <c r="M82" s="1"/>
@@ -9845,22 +10077,22 @@
       </c>
       <c r="Q82" s="1"/>
       <c r="R82" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>2</v>
       </c>
       <c r="S82" s="5">
         <v>10</v>
       </c>
       <c r="T82" s="5">
+        <f t="shared" si="25"/>
+        <v>10</v>
+      </c>
+      <c r="U82" s="1">
+        <f t="shared" si="26"/>
+        <v>6.5</v>
+      </c>
+      <c r="V82" s="1">
         <f t="shared" si="24"/>
-        <v>10</v>
-      </c>
-      <c r="U82" s="1">
-        <f t="shared" si="25"/>
-        <v>6.5</v>
-      </c>
-      <c r="V82" s="1">
-        <f t="shared" si="23"/>
         <v>1.5</v>
       </c>
       <c r="W82" s="1">
@@ -9895,10 +10127,13 @@
       </c>
       <c r="AG82" s="1"/>
       <c r="AH82" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>4</v>
       </c>
-      <c r="AI82" s="1"/>
+      <c r="AI82" s="1">
+        <f t="shared" si="28"/>
+        <v>0.7</v>
+      </c>
       <c r="AJ82" s="1"/>
       <c r="AK82" s="1"/>
       <c r="AL82" s="1"/>
@@ -9942,7 +10177,7 @@
         <v>47</v>
       </c>
       <c r="L83" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M83" s="1"/>
@@ -9953,22 +10188,22 @@
       <c r="P83" s="1"/>
       <c r="Q83" s="1"/>
       <c r="R83" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>9.4</v>
       </c>
       <c r="S83" s="5">
         <v>50</v>
       </c>
       <c r="T83" s="5">
+        <f t="shared" si="25"/>
+        <v>50</v>
+      </c>
+      <c r="U83" s="1">
+        <f t="shared" si="26"/>
+        <v>7.4468085106382977</v>
+      </c>
+      <c r="V83" s="1">
         <f t="shared" si="24"/>
-        <v>50</v>
-      </c>
-      <c r="U83" s="1">
-        <f t="shared" si="25"/>
-        <v>7.4468085106382977</v>
-      </c>
-      <c r="V83" s="1">
-        <f t="shared" si="23"/>
         <v>2.1276595744680851</v>
       </c>
       <c r="W83" s="1">
@@ -10003,10 +10238,13 @@
       </c>
       <c r="AG83" s="1"/>
       <c r="AH83" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>18</v>
       </c>
-      <c r="AI83" s="1"/>
+      <c r="AI83" s="1">
+        <f t="shared" si="28"/>
+        <v>3.29</v>
+      </c>
       <c r="AJ83" s="1"/>
       <c r="AK83" s="1"/>
       <c r="AL83" s="1"/>
@@ -10040,7 +10278,7 @@
       <c r="J84" s="9"/>
       <c r="K84" s="9"/>
       <c r="L84" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M84" s="9"/>
@@ -10051,20 +10289,20 @@
       <c r="P84" s="9"/>
       <c r="Q84" s="9"/>
       <c r="R84" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="S84" s="11"/>
       <c r="T84" s="5">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="U84" s="1" t="e">
+        <f t="shared" si="26"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V84" s="9" t="e">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="U84" s="1" t="e">
-        <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V84" s="9" t="e">
-        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W84" s="9">
@@ -10101,10 +10339,13 @@
         <v>47</v>
       </c>
       <c r="AH84" s="1">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AI84" s="1"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AI84" s="1">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AJ84" s="1"/>
       <c r="AK84" s="1"/>
       <c r="AL84" s="1"/>
@@ -10138,7 +10379,7 @@
       <c r="J85" s="9"/>
       <c r="K85" s="9"/>
       <c r="L85" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M85" s="9"/>
@@ -10149,20 +10390,20 @@
       <c r="P85" s="9"/>
       <c r="Q85" s="9"/>
       <c r="R85" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="S85" s="11"/>
       <c r="T85" s="5">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="U85" s="1" t="e">
+        <f t="shared" si="26"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V85" s="9" t="e">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="U85" s="1" t="e">
-        <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V85" s="9" t="e">
-        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W85" s="9">
@@ -10199,10 +10440,13 @@
         <v>47</v>
       </c>
       <c r="AH85" s="1">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AI85" s="1"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AI85" s="1">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AJ85" s="1"/>
       <c r="AK85" s="1"/>
       <c r="AL85" s="1"/>
@@ -10244,7 +10488,7 @@
         <v>20</v>
       </c>
       <c r="L86" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-20</v>
       </c>
       <c r="M86" s="9"/>
@@ -10255,20 +10499,20 @@
       <c r="P86" s="9"/>
       <c r="Q86" s="9"/>
       <c r="R86" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="S86" s="11"/>
       <c r="T86" s="5">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="U86" s="1" t="e">
+        <f t="shared" si="26"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V86" s="9" t="e">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="U86" s="1" t="e">
-        <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V86" s="9" t="e">
-        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W86" s="9">
@@ -10303,10 +10547,13 @@
       </c>
       <c r="AG86" s="9"/>
       <c r="AH86" s="1">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AI86" s="1"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AI86" s="1">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AJ86" s="1"/>
       <c r="AK86" s="1"/>
       <c r="AL86" s="1"/>
@@ -10350,7 +10597,7 @@
         <v>15.4</v>
       </c>
       <c r="L87" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.42999999999999972</v>
       </c>
       <c r="M87" s="1"/>
@@ -10361,23 +10608,23 @@
       <c r="P87" s="1"/>
       <c r="Q87" s="1"/>
       <c r="R87" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>3.1659999999999999</v>
       </c>
       <c r="S87" s="5">
-        <f t="shared" ref="S87:S88" si="29">11*R87-Q87-P87-O87-F87</f>
+        <f t="shared" ref="S87:S88" si="31">11*R87-Q87-P87-O87-F87</f>
         <v>17.975000000000001</v>
       </c>
       <c r="T87" s="5">
+        <f t="shared" si="25"/>
+        <v>17.975000000000001</v>
+      </c>
+      <c r="U87" s="1">
+        <f t="shared" si="26"/>
+        <v>11</v>
+      </c>
+      <c r="V87" s="1">
         <f t="shared" si="24"/>
-        <v>17.975000000000001</v>
-      </c>
-      <c r="U87" s="1">
-        <f t="shared" si="25"/>
-        <v>11</v>
-      </c>
-      <c r="V87" s="1">
-        <f t="shared" si="23"/>
         <v>5.3224889450410613</v>
       </c>
       <c r="W87" s="1">
@@ -10412,10 +10659,13 @@
       </c>
       <c r="AG87" s="1"/>
       <c r="AH87" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>18</v>
       </c>
-      <c r="AI87" s="1"/>
+      <c r="AI87" s="1">
+        <f t="shared" si="28"/>
+        <v>3.1659999999999999</v>
+      </c>
       <c r="AJ87" s="1"/>
       <c r="AK87" s="1"/>
       <c r="AL87" s="1"/>
@@ -10461,7 +10711,7 @@
         <v>209.24</v>
       </c>
       <c r="L88" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-9.1839999999999975</v>
       </c>
       <c r="M88" s="1"/>
@@ -10472,23 +10722,23 @@
       <c r="P88" s="1"/>
       <c r="Q88" s="1"/>
       <c r="R88" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>40.011200000000002</v>
       </c>
       <c r="S88" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>158.17876999999993</v>
       </c>
       <c r="T88" s="5">
+        <f t="shared" si="25"/>
+        <v>158.17876999999993</v>
+      </c>
+      <c r="U88" s="1">
+        <f t="shared" si="26"/>
+        <v>10.999999999999998</v>
+      </c>
+      <c r="V88" s="1">
         <f t="shared" si="24"/>
-        <v>158.17876999999993</v>
-      </c>
-      <c r="U88" s="1">
-        <f t="shared" si="25"/>
-        <v>10.999999999999998</v>
-      </c>
-      <c r="V88" s="1">
-        <f t="shared" si="23"/>
         <v>7.0466376914463948</v>
       </c>
       <c r="W88" s="1">
@@ -10523,10 +10773,13 @@
       </c>
       <c r="AG88" s="1"/>
       <c r="AH88" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>158</v>
       </c>
-      <c r="AI88" s="1"/>
+      <c r="AI88" s="1">
+        <f t="shared" si="28"/>
+        <v>40.011200000000002</v>
+      </c>
       <c r="AJ88" s="1"/>
       <c r="AK88" s="1"/>
       <c r="AL88" s="1"/>
@@ -10560,7 +10813,7 @@
       <c r="J89" s="9"/>
       <c r="K89" s="9"/>
       <c r="L89" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M89" s="9"/>
@@ -10571,20 +10824,20 @@
       <c r="P89" s="9"/>
       <c r="Q89" s="9"/>
       <c r="R89" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="S89" s="11"/>
       <c r="T89" s="5">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="U89" s="1" t="e">
+        <f t="shared" si="26"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V89" s="9" t="e">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="U89" s="1" t="e">
-        <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V89" s="9" t="e">
-        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W89" s="9">
@@ -10621,10 +10874,13 @@
         <v>47</v>
       </c>
       <c r="AH89" s="1">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AI89" s="1"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AI89" s="1">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AJ89" s="1"/>
       <c r="AK89" s="1"/>
       <c r="AL89" s="1"/>
@@ -10670,7 +10926,7 @@
         <v>1360.3140000000001</v>
       </c>
       <c r="L90" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-75.317999999999984</v>
       </c>
       <c r="M90" s="1"/>
@@ -10681,20 +10937,20 @@
       <c r="P90" s="1"/>
       <c r="Q90" s="1"/>
       <c r="R90" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>256.99920000000003</v>
       </c>
       <c r="S90" s="5"/>
       <c r="T90" s="5">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="U90" s="1">
+        <f t="shared" si="26"/>
+        <v>10.660212171866682</v>
+      </c>
+      <c r="V90" s="1">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="U90" s="1">
-        <f t="shared" si="25"/>
-        <v>10.660212171866682</v>
-      </c>
-      <c r="V90" s="1">
-        <f t="shared" si="23"/>
         <v>10.660212171866682</v>
       </c>
       <c r="W90" s="1">
@@ -10729,10 +10985,13 @@
       </c>
       <c r="AG90" s="1"/>
       <c r="AH90" s="1">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AI90" s="1"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AI90" s="1">
+        <f t="shared" si="28"/>
+        <v>256.99920000000003</v>
+      </c>
       <c r="AJ90" s="1"/>
       <c r="AK90" s="1"/>
       <c r="AL90" s="1"/>
@@ -10778,7 +11037,7 @@
         <v>1452.8</v>
       </c>
       <c r="L91" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>15.843000000000075</v>
       </c>
       <c r="M91" s="1"/>
@@ -10791,7 +11050,7 @@
         <v>200</v>
       </c>
       <c r="R91" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>293.72860000000003</v>
       </c>
       <c r="S91" s="5">
@@ -10799,15 +11058,15 @@
         <v>1537.067</v>
       </c>
       <c r="T91" s="5">
-        <f t="shared" ref="T91:T92" si="30">S91+$T$1*R91</f>
+        <f t="shared" ref="T91:T92" si="32">S91+$T$1*R91</f>
         <v>1331.4569799999999</v>
       </c>
       <c r="U91" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>9.2999999999999989</v>
       </c>
       <c r="V91" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>4.7670502634064231</v>
       </c>
       <c r="W91" s="1">
@@ -10842,10 +11101,13 @@
       </c>
       <c r="AG91" s="1"/>
       <c r="AH91" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>1331</v>
       </c>
-      <c r="AI91" s="1"/>
+      <c r="AI91" s="1">
+        <f t="shared" si="28"/>
+        <v>293.72860000000003</v>
+      </c>
       <c r="AJ91" s="1"/>
       <c r="AK91" s="1"/>
       <c r="AL91" s="1"/>
@@ -10891,7 +11153,7 @@
         <v>2397.5</v>
       </c>
       <c r="L92" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-73.907000000000153</v>
       </c>
       <c r="M92" s="1"/>
@@ -10904,7 +11166,7 @@
         <v>240</v>
       </c>
       <c r="R92" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>464.71859999999998</v>
       </c>
       <c r="S92" s="5">
@@ -10912,15 +11174,15 @@
         <v>1291.5119999999997</v>
       </c>
       <c r="T92" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>966.20897999999977</v>
       </c>
       <c r="U92" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>9.2999999999999989</v>
       </c>
       <c r="V92" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>7.2208730186396677</v>
       </c>
       <c r="W92" s="1">
@@ -10955,10 +11217,13 @@
       </c>
       <c r="AG92" s="1"/>
       <c r="AH92" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>966</v>
       </c>
-      <c r="AI92" s="1"/>
+      <c r="AI92" s="1">
+        <f t="shared" si="28"/>
+        <v>464.71859999999998</v>
+      </c>
       <c r="AJ92" s="1"/>
       <c r="AK92" s="1"/>
       <c r="AL92" s="1"/>
@@ -10992,7 +11257,7 @@
       <c r="J93" s="9"/>
       <c r="K93" s="9"/>
       <c r="L93" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M93" s="9"/>
@@ -11003,20 +11268,20 @@
       <c r="P93" s="9"/>
       <c r="Q93" s="9"/>
       <c r="R93" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="S93" s="11"/>
       <c r="T93" s="5">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="U93" s="1" t="e">
+        <f t="shared" si="26"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V93" s="9" t="e">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="U93" s="1" t="e">
-        <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V93" s="9" t="e">
-        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W93" s="9">
@@ -11053,10 +11318,13 @@
         <v>47</v>
       </c>
       <c r="AH93" s="1">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AI93" s="1"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AI93" s="1">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AJ93" s="1"/>
       <c r="AK93" s="1"/>
       <c r="AL93" s="1"/>
@@ -11100,7 +11368,7 @@
         <v>4</v>
       </c>
       <c r="L94" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-9</v>
       </c>
       <c r="M94" s="1"/>
@@ -11113,7 +11381,7 @@
       </c>
       <c r="Q94" s="1"/>
       <c r="R94" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-1</v>
       </c>
       <c r="S94" s="5">
@@ -11124,11 +11392,11 @@
         <v>70</v>
       </c>
       <c r="U94" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>-59</v>
       </c>
       <c r="V94" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>11</v>
       </c>
       <c r="W94" s="1">
@@ -11163,10 +11431,13 @@
       </c>
       <c r="AG94" s="1"/>
       <c r="AH94" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>21</v>
       </c>
-      <c r="AI94" s="1"/>
+      <c r="AI94" s="1">
+        <f t="shared" si="28"/>
+        <v>-0.3</v>
+      </c>
       <c r="AJ94" s="1"/>
       <c r="AK94" s="1"/>
       <c r="AL94" s="1"/>
@@ -11200,7 +11471,7 @@
       <c r="J95" s="9"/>
       <c r="K95" s="9"/>
       <c r="L95" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M95" s="9"/>
@@ -11211,20 +11482,20 @@
       <c r="P95" s="9"/>
       <c r="Q95" s="9"/>
       <c r="R95" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="S95" s="11"/>
       <c r="T95" s="5">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="U95" s="1" t="e">
+        <f t="shared" si="26"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V95" s="9" t="e">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="U95" s="1" t="e">
-        <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V95" s="9" t="e">
-        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W95" s="9">
@@ -11261,10 +11532,13 @@
         <v>47</v>
       </c>
       <c r="AH95" s="1">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AI95" s="1"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AI95" s="1">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AJ95" s="1"/>
       <c r="AK95" s="1"/>
       <c r="AL95" s="1"/>
@@ -11310,7 +11584,7 @@
         <v>101</v>
       </c>
       <c r="L96" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-10</v>
       </c>
       <c r="M96" s="1"/>
@@ -11323,22 +11597,22 @@
       </c>
       <c r="Q96" s="1"/>
       <c r="R96" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>18.2</v>
       </c>
       <c r="S96" s="5">
         <v>40</v>
       </c>
       <c r="T96" s="5">
+        <f t="shared" si="25"/>
+        <v>40</v>
+      </c>
+      <c r="U96" s="1">
+        <f t="shared" si="26"/>
+        <v>3.5551648351648342</v>
+      </c>
+      <c r="V96" s="1">
         <f t="shared" si="24"/>
-        <v>40</v>
-      </c>
-      <c r="U96" s="1">
-        <f t="shared" si="25"/>
-        <v>3.5551648351648342</v>
-      </c>
-      <c r="V96" s="1">
-        <f t="shared" si="23"/>
         <v>1.3573626373626362</v>
       </c>
       <c r="W96" s="1">
@@ -11373,10 +11647,13 @@
       </c>
       <c r="AG96" s="1"/>
       <c r="AH96" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>3</v>
       </c>
-      <c r="AI96" s="1"/>
+      <c r="AI96" s="1">
+        <f t="shared" si="28"/>
+        <v>1.274</v>
+      </c>
       <c r="AJ96" s="1"/>
       <c r="AK96" s="1"/>
       <c r="AL96" s="1"/>
@@ -11412,7 +11689,7 @@
       <c r="J97" s="1"/>
       <c r="K97" s="1"/>
       <c r="L97" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M97" s="1"/>
@@ -11423,22 +11700,22 @@
       <c r="P97" s="1"/>
       <c r="Q97" s="1"/>
       <c r="R97" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="S97" s="5">
         <v>30</v>
       </c>
       <c r="T97" s="5">
+        <f t="shared" si="25"/>
+        <v>30</v>
+      </c>
+      <c r="U97" s="1" t="e">
+        <f t="shared" si="26"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V97" s="1" t="e">
         <f t="shared" si="24"/>
-        <v>30</v>
-      </c>
-      <c r="U97" s="1" t="e">
-        <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V97" s="1" t="e">
-        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W97" s="1">
@@ -11473,10 +11750,13 @@
       </c>
       <c r="AG97" s="1"/>
       <c r="AH97" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>2</v>
       </c>
-      <c r="AI97" s="1"/>
+      <c r="AI97" s="1">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AJ97" s="1"/>
       <c r="AK97" s="1"/>
       <c r="AL97" s="1"/>
@@ -11522,7 +11802,7 @@
         <v>104</v>
       </c>
       <c r="L98" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-18</v>
       </c>
       <c r="M98" s="1"/>
@@ -11533,23 +11813,23 @@
       <c r="P98" s="1"/>
       <c r="Q98" s="1"/>
       <c r="R98" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>17.2</v>
       </c>
       <c r="S98" s="5">
-        <f t="shared" ref="S98" si="31">11*R98-Q98-P98-O98-F98</f>
+        <f t="shared" ref="S98" si="33">11*R98-Q98-P98-O98-F98</f>
         <v>107.18999999999998</v>
       </c>
       <c r="T98" s="5">
+        <f t="shared" si="25"/>
+        <v>107.18999999999998</v>
+      </c>
+      <c r="U98" s="1">
+        <f t="shared" si="26"/>
+        <v>11</v>
+      </c>
+      <c r="V98" s="1">
         <f t="shared" si="24"/>
-        <v>107.18999999999998</v>
-      </c>
-      <c r="U98" s="1">
-        <f t="shared" si="25"/>
-        <v>11</v>
-      </c>
-      <c r="V98" s="1">
-        <f t="shared" si="23"/>
         <v>4.7680232558139544</v>
       </c>
       <c r="W98" s="1">
@@ -11584,10 +11864,13 @@
       </c>
       <c r="AG98" s="1"/>
       <c r="AH98" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>8</v>
       </c>
-      <c r="AI98" s="1"/>
+      <c r="AI98" s="1">
+        <f t="shared" si="28"/>
+        <v>1.204</v>
+      </c>
       <c r="AJ98" s="1"/>
       <c r="AK98" s="1"/>
       <c r="AL98" s="1"/>
@@ -11631,7 +11914,7 @@
         <v>24</v>
       </c>
       <c r="L99" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-25</v>
       </c>
       <c r="M99" s="9"/>
@@ -11642,20 +11925,20 @@
       <c r="P99" s="9"/>
       <c r="Q99" s="9"/>
       <c r="R99" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-0.2</v>
       </c>
       <c r="S99" s="11"/>
       <c r="T99" s="5">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="U99" s="1">
+        <f t="shared" si="26"/>
+        <v>-35</v>
+      </c>
+      <c r="V99" s="9">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="U99" s="1">
-        <f t="shared" si="25"/>
-        <v>-35</v>
-      </c>
-      <c r="V99" s="9">
-        <f t="shared" si="23"/>
         <v>-35</v>
       </c>
       <c r="W99" s="9">
@@ -11690,10 +11973,13 @@
       </c>
       <c r="AG99" s="9"/>
       <c r="AH99" s="1">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AI99" s="1"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AI99" s="1">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AJ99" s="1"/>
       <c r="AK99" s="1"/>
       <c r="AL99" s="1"/>
@@ -11733,7 +12019,7 @@
         <v>3</v>
       </c>
       <c r="L100" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-3</v>
       </c>
       <c r="M100" s="9"/>
@@ -11744,20 +12030,20 @@
       <c r="P100" s="9"/>
       <c r="Q100" s="9"/>
       <c r="R100" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="S100" s="11"/>
       <c r="T100" s="5">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="U100" s="1" t="e">
+        <f t="shared" si="26"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V100" s="9" t="e">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="U100" s="1" t="e">
-        <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V100" s="9" t="e">
-        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W100" s="9">
@@ -11794,10 +12080,13 @@
         <v>140</v>
       </c>
       <c r="AH100" s="1">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AI100" s="1"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AI100" s="1">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AJ100" s="1"/>
       <c r="AK100" s="1"/>
       <c r="AL100" s="1"/>
@@ -11831,7 +12120,7 @@
       <c r="J101" s="9"/>
       <c r="K101" s="9"/>
       <c r="L101" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M101" s="9"/>
@@ -11842,20 +12131,20 @@
       <c r="P101" s="9"/>
       <c r="Q101" s="9"/>
       <c r="R101" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="S101" s="11"/>
       <c r="T101" s="5">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="U101" s="1" t="e">
+        <f t="shared" si="26"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V101" s="9" t="e">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="U101" s="1" t="e">
-        <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V101" s="9" t="e">
-        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W101" s="9">
@@ -11892,10 +12181,13 @@
         <v>47</v>
       </c>
       <c r="AH101" s="1">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AI101" s="1"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AI101" s="1">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AJ101" s="1"/>
       <c r="AK101" s="1"/>
       <c r="AL101" s="1"/>
@@ -11935,7 +12227,7 @@
         <v>1</v>
       </c>
       <c r="L102" s="9">
-        <f t="shared" ref="L102:L133" si="32">E102-K102</f>
+        <f t="shared" ref="L102:L133" si="34">E102-K102</f>
         <v>-1</v>
       </c>
       <c r="M102" s="9"/>
@@ -11946,20 +12238,20 @@
       <c r="P102" s="9"/>
       <c r="Q102" s="9"/>
       <c r="R102" s="9">
-        <f t="shared" ref="R102:R133" si="33">E102/5</f>
+        <f t="shared" ref="R102:R133" si="35">E102/5</f>
         <v>0</v>
       </c>
       <c r="S102" s="11"/>
       <c r="T102" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="U102" s="1" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V102" s="9" t="e">
-        <f t="shared" ref="V102:V133" si="34">(F102+O102+P102+Q102)/R102</f>
+        <f t="shared" ref="V102:V133" si="36">(F102+O102+P102+Q102)/R102</f>
         <v>#DIV/0!</v>
       </c>
       <c r="W102" s="9">
@@ -11996,10 +12288,13 @@
         <v>47</v>
       </c>
       <c r="AH102" s="1">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AI102" s="1"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AI102" s="1">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AJ102" s="1"/>
       <c r="AK102" s="1"/>
       <c r="AL102" s="1"/>
@@ -12033,7 +12328,7 @@
       <c r="J103" s="9"/>
       <c r="K103" s="9"/>
       <c r="L103" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M103" s="9"/>
@@ -12044,20 +12339,20 @@
       <c r="P103" s="9"/>
       <c r="Q103" s="9"/>
       <c r="R103" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="S103" s="11"/>
       <c r="T103" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="U103" s="1" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V103" s="9" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W103" s="9">
@@ -12094,10 +12389,13 @@
         <v>47</v>
       </c>
       <c r="AH103" s="1">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AI103" s="1"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AI103" s="1">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AJ103" s="1"/>
       <c r="AK103" s="1"/>
       <c r="AL103" s="1"/>
@@ -12131,7 +12429,7 @@
       <c r="J104" s="9"/>
       <c r="K104" s="9"/>
       <c r="L104" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M104" s="9"/>
@@ -12142,20 +12440,20 @@
       <c r="P104" s="9"/>
       <c r="Q104" s="9"/>
       <c r="R104" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="S104" s="11"/>
       <c r="T104" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="U104" s="1" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V104" s="9" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W104" s="9">
@@ -12192,10 +12490,13 @@
         <v>47</v>
       </c>
       <c r="AH104" s="1">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AI104" s="1"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AI104" s="1">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AJ104" s="1"/>
       <c r="AK104" s="1"/>
       <c r="AL104" s="1"/>
@@ -12241,7 +12542,7 @@
         <v>121</v>
       </c>
       <c r="L105" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-3</v>
       </c>
       <c r="M105" s="1"/>
@@ -12252,23 +12553,23 @@
       <c r="P105" s="1"/>
       <c r="Q105" s="1"/>
       <c r="R105" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>23.6</v>
       </c>
       <c r="S105" s="5">
-        <f t="shared" ref="S105" si="35">11*R105-Q105-P105-O105-F105</f>
+        <f t="shared" ref="S105" si="37">11*R105-Q105-P105-O105-F105</f>
         <v>143.97000000000003</v>
       </c>
       <c r="T105" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>143.97000000000003</v>
       </c>
       <c r="U105" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>11</v>
       </c>
       <c r="V105" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>4.8995762711864401</v>
       </c>
       <c r="W105" s="1">
@@ -12303,10 +12604,13 @@
       </c>
       <c r="AG105" s="1"/>
       <c r="AH105" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>12</v>
       </c>
-      <c r="AI105" s="1"/>
+      <c r="AI105" s="1">
+        <f t="shared" si="28"/>
+        <v>1.8880000000000001</v>
+      </c>
       <c r="AJ105" s="1"/>
       <c r="AK105" s="1"/>
       <c r="AL105" s="1"/>
@@ -12352,7 +12656,7 @@
         <v>122</v>
       </c>
       <c r="L106" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-11</v>
       </c>
       <c r="M106" s="1"/>
@@ -12363,7 +12667,7 @@
       <c r="P106" s="1"/>
       <c r="Q106" s="1"/>
       <c r="R106" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>22.2</v>
       </c>
       <c r="S106" s="5">
@@ -12371,15 +12675,15 @@
         <v>131.19999999999999</v>
       </c>
       <c r="T106" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>131.19999999999999</v>
       </c>
       <c r="U106" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>10</v>
       </c>
       <c r="V106" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>4.0900900900900909</v>
       </c>
       <c r="W106" s="1">
@@ -12414,10 +12718,13 @@
       </c>
       <c r="AG106" s="1"/>
       <c r="AH106" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>10</v>
       </c>
-      <c r="AI106" s="1"/>
+      <c r="AI106" s="1">
+        <f t="shared" si="28"/>
+        <v>1.776</v>
+      </c>
       <c r="AJ106" s="1"/>
       <c r="AK106" s="1"/>
       <c r="AL106" s="1"/>
@@ -12451,7 +12758,7 @@
       <c r="J107" s="9"/>
       <c r="K107" s="9"/>
       <c r="L107" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M107" s="9"/>
@@ -12462,20 +12769,20 @@
       <c r="P107" s="9"/>
       <c r="Q107" s="9"/>
       <c r="R107" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="S107" s="11"/>
       <c r="T107" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="U107" s="1" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V107" s="9" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W107" s="9">
@@ -12512,10 +12819,13 @@
         <v>47</v>
       </c>
       <c r="AH107" s="1">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AI107" s="1"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AI107" s="1">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AJ107" s="1"/>
       <c r="AK107" s="1"/>
       <c r="AL107" s="1"/>
@@ -12561,7 +12871,7 @@
         <v>197.75</v>
       </c>
       <c r="L108" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-9.717000000000013</v>
       </c>
       <c r="M108" s="1"/>
@@ -12574,22 +12884,22 @@
       </c>
       <c r="Q108" s="1"/>
       <c r="R108" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>37.6066</v>
       </c>
       <c r="S108" s="5">
         <v>120</v>
       </c>
       <c r="T108" s="5">
-        <f t="shared" ref="T108:T110" si="36">S108*0.7</f>
+        <f t="shared" ref="T108:T110" si="38">S108*0.7</f>
         <v>84</v>
       </c>
       <c r="U108" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>2.1858929017778794</v>
       </c>
       <c r="V108" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>-4.7757574468311394E-2</v>
       </c>
       <c r="W108" s="1">
@@ -12624,10 +12934,13 @@
       </c>
       <c r="AG108" s="1"/>
       <c r="AH108" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>84</v>
       </c>
-      <c r="AI108" s="1"/>
+      <c r="AI108" s="1">
+        <f t="shared" si="28"/>
+        <v>37.6066</v>
+      </c>
       <c r="AJ108" s="1"/>
       <c r="AK108" s="1"/>
       <c r="AL108" s="1"/>
@@ -12673,7 +12986,7 @@
         <v>200.85</v>
       </c>
       <c r="L109" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>8.8520000000000039</v>
       </c>
       <c r="M109" s="1"/>
@@ -12684,22 +12997,22 @@
       <c r="P109" s="1"/>
       <c r="Q109" s="1"/>
       <c r="R109" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>41.940399999999997</v>
       </c>
       <c r="S109" s="5">
         <v>190</v>
       </c>
       <c r="T109" s="5">
+        <f t="shared" si="38"/>
+        <v>133</v>
+      </c>
+      <c r="U109" s="1">
+        <f t="shared" si="26"/>
+        <v>4.2573032207608899</v>
+      </c>
+      <c r="V109" s="1">
         <f t="shared" si="36"/>
-        <v>133</v>
-      </c>
-      <c r="U109" s="1">
-        <f t="shared" si="25"/>
-        <v>4.2573032207608899</v>
-      </c>
-      <c r="V109" s="1">
-        <f t="shared" si="34"/>
         <v>1.086136517534406</v>
       </c>
       <c r="W109" s="1">
@@ -12734,10 +13047,13 @@
       </c>
       <c r="AG109" s="1"/>
       <c r="AH109" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>133</v>
       </c>
-      <c r="AI109" s="1"/>
+      <c r="AI109" s="1">
+        <f t="shared" si="28"/>
+        <v>41.940399999999997</v>
+      </c>
       <c r="AJ109" s="1"/>
       <c r="AK109" s="1"/>
       <c r="AL109" s="1"/>
@@ -12781,7 +13097,7 @@
         <v>262.45</v>
       </c>
       <c r="L110" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-268.791</v>
       </c>
       <c r="M110" s="1"/>
@@ -12794,22 +13110,22 @@
       </c>
       <c r="Q110" s="1"/>
       <c r="R110" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>-1.2682</v>
       </c>
       <c r="S110" s="5">
         <v>150</v>
       </c>
       <c r="T110" s="5">
+        <f t="shared" si="38"/>
+        <v>105</v>
+      </c>
+      <c r="U110" s="1">
+        <f t="shared" si="26"/>
+        <v>-87.56662986910581</v>
+      </c>
+      <c r="V110" s="1">
         <f t="shared" si="36"/>
-        <v>105</v>
-      </c>
-      <c r="U110" s="1">
-        <f t="shared" si="25"/>
-        <v>-87.56662986910581</v>
-      </c>
-      <c r="V110" s="1">
-        <f t="shared" si="34"/>
         <v>-4.7721179624664876</v>
       </c>
       <c r="W110" s="1">
@@ -12844,10 +13160,13 @@
       </c>
       <c r="AG110" s="1"/>
       <c r="AH110" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>105</v>
       </c>
-      <c r="AI110" s="1"/>
+      <c r="AI110" s="1">
+        <f t="shared" si="28"/>
+        <v>-1.2682</v>
+      </c>
       <c r="AJ110" s="1"/>
       <c r="AK110" s="1"/>
       <c r="AL110" s="1"/>
@@ -12881,7 +13200,7 @@
       <c r="J111" s="9"/>
       <c r="K111" s="9"/>
       <c r="L111" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M111" s="9"/>
@@ -12892,20 +13211,20 @@
       <c r="P111" s="9"/>
       <c r="Q111" s="9"/>
       <c r="R111" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="S111" s="11"/>
       <c r="T111" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="U111" s="1" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V111" s="9" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W111" s="9">
@@ -12942,10 +13261,13 @@
         <v>47</v>
       </c>
       <c r="AH111" s="1">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AI111" s="1"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AI111" s="1">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AJ111" s="1"/>
       <c r="AK111" s="1"/>
       <c r="AL111" s="1"/>
@@ -12979,7 +13301,7 @@
       <c r="J112" s="9"/>
       <c r="K112" s="9"/>
       <c r="L112" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M112" s="9"/>
@@ -12990,20 +13312,20 @@
       <c r="P112" s="9"/>
       <c r="Q112" s="9"/>
       <c r="R112" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="S112" s="11"/>
       <c r="T112" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="U112" s="1" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V112" s="9" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W112" s="9">
@@ -13040,10 +13362,13 @@
         <v>47</v>
       </c>
       <c r="AH112" s="1">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AI112" s="1"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AI112" s="1">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AJ112" s="1"/>
       <c r="AK112" s="1"/>
       <c r="AL112" s="1"/>
@@ -13089,7 +13414,7 @@
         <v>345</v>
       </c>
       <c r="L113" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-62</v>
       </c>
       <c r="M113" s="1"/>
@@ -13102,22 +13427,22 @@
       </c>
       <c r="Q113" s="1"/>
       <c r="R113" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>56.6</v>
       </c>
       <c r="S113" s="5">
         <v>150</v>
       </c>
       <c r="T113" s="5">
-        <f t="shared" ref="T113:T115" si="37">S113*0.7</f>
+        <f t="shared" ref="T113:T115" si="39">S113*0.7</f>
         <v>105</v>
       </c>
       <c r="U113" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1.918197879858657</v>
       </c>
       <c r="V113" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>6.3074204946996351E-2</v>
       </c>
       <c r="W113" s="1">
@@ -13152,10 +13477,13 @@
       </c>
       <c r="AG113" s="1"/>
       <c r="AH113" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>29</v>
       </c>
-      <c r="AI113" s="1"/>
+      <c r="AI113" s="1">
+        <f t="shared" si="28"/>
+        <v>15.848000000000003</v>
+      </c>
       <c r="AJ113" s="1"/>
       <c r="AK113" s="1"/>
       <c r="AL113" s="1"/>
@@ -13199,7 +13527,7 @@
         <v>52</v>
       </c>
       <c r="L114" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-64</v>
       </c>
       <c r="M114" s="1"/>
@@ -13212,22 +13540,22 @@
       </c>
       <c r="Q114" s="1"/>
       <c r="R114" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>-2.4</v>
       </c>
       <c r="S114" s="5">
         <v>100</v>
       </c>
       <c r="T114" s="5">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>70</v>
       </c>
       <c r="U114" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>-28.75</v>
       </c>
       <c r="V114" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0.41666666666666374</v>
       </c>
       <c r="W114" s="1">
@@ -13262,10 +13590,13 @@
       </c>
       <c r="AG114" s="1"/>
       <c r="AH114" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>20</v>
       </c>
-      <c r="AI114" s="1"/>
+      <c r="AI114" s="1">
+        <f t="shared" si="28"/>
+        <v>-0.67200000000000004</v>
+      </c>
       <c r="AJ114" s="1"/>
       <c r="AK114" s="1"/>
       <c r="AL114" s="1"/>
@@ -13311,7 +13642,7 @@
         <v>343</v>
       </c>
       <c r="L115" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-2</v>
       </c>
       <c r="M115" s="1"/>
@@ -13324,22 +13655,22 @@
       </c>
       <c r="Q115" s="1"/>
       <c r="R115" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>68.2</v>
       </c>
       <c r="S115" s="5">
         <v>100</v>
       </c>
       <c r="T115" s="5">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>70</v>
       </c>
       <c r="U115" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.91642228739002929</v>
       </c>
       <c r="V115" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>-0.10997067448680352</v>
       </c>
       <c r="W115" s="1">
@@ -13374,10 +13705,13 @@
       </c>
       <c r="AG115" s="1"/>
       <c r="AH115" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>20</v>
       </c>
-      <c r="AI115" s="1"/>
+      <c r="AI115" s="1">
+        <f t="shared" si="28"/>
+        <v>19.096000000000004</v>
+      </c>
       <c r="AJ115" s="1"/>
       <c r="AK115" s="1"/>
       <c r="AL115" s="1"/>
@@ -13411,7 +13745,7 @@
       <c r="J116" s="9"/>
       <c r="K116" s="9"/>
       <c r="L116" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M116" s="9"/>
@@ -13422,20 +13756,20 @@
       <c r="P116" s="9"/>
       <c r="Q116" s="9"/>
       <c r="R116" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="S116" s="11"/>
       <c r="T116" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="U116" s="1" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V116" s="9" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W116" s="9">
@@ -13472,10 +13806,13 @@
         <v>47</v>
       </c>
       <c r="AH116" s="1">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AI116" s="1"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AI116" s="1">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AJ116" s="1"/>
       <c r="AK116" s="1"/>
       <c r="AL116" s="1"/>
@@ -13521,7 +13858,7 @@
         <v>37.5</v>
       </c>
       <c r="L117" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-5.8329999999999984</v>
       </c>
       <c r="M117" s="1"/>
@@ -13532,20 +13869,20 @@
       <c r="P117" s="1"/>
       <c r="Q117" s="1"/>
       <c r="R117" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>6.3334000000000001</v>
       </c>
       <c r="S117" s="5"/>
       <c r="T117" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="U117" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>28.719645056367828</v>
       </c>
       <c r="V117" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>28.719645056367828</v>
       </c>
       <c r="W117" s="1">
@@ -13582,10 +13919,13 @@
         <v>88</v>
       </c>
       <c r="AH117" s="1">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AI117" s="1"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AI117" s="1">
+        <f t="shared" si="28"/>
+        <v>6.3334000000000001</v>
+      </c>
       <c r="AJ117" s="1"/>
       <c r="AK117" s="1"/>
       <c r="AL117" s="1"/>
@@ -13631,7 +13971,7 @@
         <v>32</v>
       </c>
       <c r="L118" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.29500000000000171</v>
       </c>
       <c r="M118" s="1"/>
@@ -13642,23 +13982,23 @@
       <c r="P118" s="1"/>
       <c r="Q118" s="1"/>
       <c r="R118" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>6.4590000000000005</v>
       </c>
       <c r="S118" s="5">
-        <f t="shared" ref="S118" si="38">11*R118-Q118-P118-O118-F118</f>
+        <f t="shared" ref="S118" si="40">11*R118-Q118-P118-O118-F118</f>
         <v>13.613000000000007</v>
       </c>
       <c r="T118" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>13.613000000000007</v>
       </c>
       <c r="U118" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>11</v>
       </c>
       <c r="V118" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>8.8923982040563541</v>
       </c>
       <c r="W118" s="1">
@@ -13693,10 +14033,13 @@
       </c>
       <c r="AG118" s="1"/>
       <c r="AH118" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>14</v>
       </c>
-      <c r="AI118" s="1"/>
+      <c r="AI118" s="1">
+        <f t="shared" si="28"/>
+        <v>6.4590000000000005</v>
+      </c>
       <c r="AJ118" s="1"/>
       <c r="AK118" s="1"/>
       <c r="AL118" s="1"/>
@@ -13730,7 +14073,7 @@
       <c r="J119" s="9"/>
       <c r="K119" s="9"/>
       <c r="L119" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M119" s="9"/>
@@ -13741,20 +14084,20 @@
       <c r="P119" s="9"/>
       <c r="Q119" s="9"/>
       <c r="R119" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="S119" s="11"/>
       <c r="T119" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="U119" s="1" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V119" s="9" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W119" s="9">
@@ -13791,10 +14134,13 @@
         <v>47</v>
       </c>
       <c r="AH119" s="1">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AI119" s="1"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AI119" s="1">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AJ119" s="1"/>
       <c r="AK119" s="1"/>
       <c r="AL119" s="1"/>
@@ -13828,7 +14174,7 @@
       <c r="J120" s="9"/>
       <c r="K120" s="9"/>
       <c r="L120" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M120" s="9"/>
@@ -13839,20 +14185,20 @@
       <c r="P120" s="9"/>
       <c r="Q120" s="9"/>
       <c r="R120" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="S120" s="11"/>
       <c r="T120" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="U120" s="1" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V120" s="9" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W120" s="9">
@@ -13889,10 +14235,13 @@
         <v>47</v>
       </c>
       <c r="AH120" s="1">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AI120" s="1"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AI120" s="1">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AJ120" s="1"/>
       <c r="AK120" s="1"/>
       <c r="AL120" s="1"/>
@@ -13938,7 +14287,7 @@
         <v>105.4</v>
       </c>
       <c r="L121" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-1.0220000000000056</v>
       </c>
       <c r="M121" s="1"/>
@@ -13949,23 +14298,23 @@
       <c r="P121" s="1"/>
       <c r="Q121" s="1"/>
       <c r="R121" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>20.875599999999999</v>
       </c>
       <c r="S121" s="5">
-        <f t="shared" ref="S121:S124" si="39">11*R121-Q121-P121-O121-F121</f>
+        <f t="shared" ref="S121:S124" si="41">11*R121-Q121-P121-O121-F121</f>
         <v>9.8856799999999936</v>
       </c>
       <c r="T121" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>9.8856799999999936</v>
       </c>
       <c r="U121" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>11</v>
       </c>
       <c r="V121" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>10.52644810209048</v>
       </c>
       <c r="W121" s="1">
@@ -14000,10 +14349,13 @@
       </c>
       <c r="AG121" s="1"/>
       <c r="AH121" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>10</v>
       </c>
-      <c r="AI121" s="1"/>
+      <c r="AI121" s="1">
+        <f t="shared" si="28"/>
+        <v>20.875599999999999</v>
+      </c>
       <c r="AJ121" s="1"/>
       <c r="AK121" s="1"/>
       <c r="AL121" s="1"/>
@@ -14049,7 +14401,7 @@
         <v>283.90699999999998</v>
       </c>
       <c r="L122" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>1.9879999999999995</v>
       </c>
       <c r="M122" s="1"/>
@@ -14060,23 +14412,23 @@
       <c r="P122" s="1"/>
       <c r="Q122" s="1"/>
       <c r="R122" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>57.178999999999995</v>
       </c>
       <c r="S122" s="5">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>351.75104599999986</v>
       </c>
       <c r="T122" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>351.75104599999986</v>
       </c>
       <c r="U122" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>11</v>
       </c>
       <c r="V122" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>4.8482476783434496</v>
       </c>
       <c r="W122" s="1">
@@ -14111,10 +14463,13 @@
       </c>
       <c r="AG122" s="1"/>
       <c r="AH122" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>352</v>
       </c>
-      <c r="AI122" s="1"/>
+      <c r="AI122" s="1">
+        <f t="shared" si="28"/>
+        <v>57.178999999999995</v>
+      </c>
       <c r="AJ122" s="1"/>
       <c r="AK122" s="1"/>
       <c r="AL122" s="1"/>
@@ -14158,7 +14513,7 @@
         <v>59.2</v>
       </c>
       <c r="L123" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>7.7259999999999991</v>
       </c>
       <c r="M123" s="1"/>
@@ -14169,23 +14524,23 @@
       <c r="P123" s="1"/>
       <c r="Q123" s="1"/>
       <c r="R123" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>13.385200000000001</v>
       </c>
       <c r="S123" s="5">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>43.266097999999985</v>
       </c>
       <c r="T123" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>43.266097999999985</v>
       </c>
       <c r="U123" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>11</v>
       </c>
       <c r="V123" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>7.7676166213429765</v>
       </c>
       <c r="W123" s="1">
@@ -14220,10 +14575,13 @@
       </c>
       <c r="AG123" s="1"/>
       <c r="AH123" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>43</v>
       </c>
-      <c r="AI123" s="1"/>
+      <c r="AI123" s="1">
+        <f t="shared" si="28"/>
+        <v>13.385200000000001</v>
+      </c>
       <c r="AJ123" s="1"/>
       <c r="AK123" s="1"/>
       <c r="AL123" s="1"/>
@@ -14269,7 +14627,7 @@
         <v>822</v>
       </c>
       <c r="L124" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-2.8999999999999773</v>
       </c>
       <c r="M124" s="1"/>
@@ -14282,11 +14640,11 @@
         <v>110</v>
       </c>
       <c r="R124" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>163.82</v>
       </c>
       <c r="S124" s="5">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>711.44485400000087</v>
       </c>
       <c r="T124" s="5">
@@ -14294,11 +14652,11 @@
         <v>596.7708540000009</v>
       </c>
       <c r="U124" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>10.3</v>
       </c>
       <c r="V124" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>6.6571550848492187</v>
       </c>
       <c r="W124" s="1">
@@ -14333,10 +14691,13 @@
       </c>
       <c r="AG124" s="1"/>
       <c r="AH124" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>597</v>
       </c>
-      <c r="AI124" s="1"/>
+      <c r="AI124" s="1">
+        <f t="shared" si="28"/>
+        <v>163.82</v>
+      </c>
       <c r="AJ124" s="1"/>
       <c r="AK124" s="1"/>
       <c r="AL124" s="1"/>
@@ -14378,7 +14739,7 @@
         <v>10</v>
       </c>
       <c r="L125" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-10</v>
       </c>
       <c r="M125" s="1"/>
@@ -14389,22 +14750,22 @@
       <c r="P125" s="1"/>
       <c r="Q125" s="1"/>
       <c r="R125" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="S125" s="5">
         <v>100</v>
       </c>
       <c r="T125" s="5">
-        <f t="shared" ref="T125:T126" si="40">S125*0.7</f>
+        <f t="shared" ref="T125:T126" si="42">S125*0.7</f>
         <v>70</v>
       </c>
       <c r="U125" s="1" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V125" s="1" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W125" s="1">
@@ -14441,10 +14802,13 @@
         <v>166</v>
       </c>
       <c r="AH125" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>18</v>
       </c>
-      <c r="AI125" s="1"/>
+      <c r="AI125" s="1">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AJ125" s="1"/>
       <c r="AK125" s="1"/>
       <c r="AL125" s="1"/>
@@ -14486,7 +14850,7 @@
       <c r="J126" s="1"/>
       <c r="K126" s="1"/>
       <c r="L126" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>2</v>
       </c>
       <c r="M126" s="1"/>
@@ -14497,22 +14861,22 @@
       <c r="P126" s="1"/>
       <c r="Q126" s="1"/>
       <c r="R126" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0.4</v>
       </c>
       <c r="S126" s="5">
         <v>100</v>
       </c>
       <c r="T126" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>70</v>
       </c>
       <c r="U126" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>255</v>
       </c>
       <c r="V126" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>80</v>
       </c>
       <c r="W126" s="1">
@@ -14549,10 +14913,13 @@
         <v>166</v>
       </c>
       <c r="AH126" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>23</v>
       </c>
-      <c r="AI126" s="1"/>
+      <c r="AI126" s="1">
+        <f t="shared" si="28"/>
+        <v>0.13</v>
+      </c>
       <c r="AJ126" s="1"/>
       <c r="AK126" s="1"/>
       <c r="AL126" s="1"/>
@@ -14598,7 +14965,7 @@
         <v>265</v>
       </c>
       <c r="L127" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-2</v>
       </c>
       <c r="M127" s="1"/>
@@ -14609,7 +14976,7 @@
       <c r="P127" s="1"/>
       <c r="Q127" s="1"/>
       <c r="R127" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>52.6</v>
       </c>
       <c r="S127" s="5">
@@ -14617,15 +14984,15 @@
         <v>317</v>
       </c>
       <c r="T127" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>317</v>
       </c>
       <c r="U127" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>10</v>
       </c>
       <c r="V127" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>3.9733840304182508</v>
       </c>
       <c r="W127" s="1">
@@ -14662,10 +15029,13 @@
         <v>166</v>
       </c>
       <c r="AH127" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>79</v>
       </c>
-      <c r="AI127" s="1"/>
+      <c r="AI127" s="1">
+        <f t="shared" si="28"/>
+        <v>13.15</v>
+      </c>
       <c r="AJ127" s="1"/>
       <c r="AK127" s="1"/>
       <c r="AL127" s="1"/>
@@ -14703,7 +15073,7 @@
         <v>2</v>
       </c>
       <c r="L128" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-2</v>
       </c>
       <c r="M128" s="1"/>
@@ -14716,7 +15086,7 @@
       </c>
       <c r="Q128" s="1"/>
       <c r="R128" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="S128" s="5">
@@ -14727,11 +15097,11 @@
         <v>105</v>
       </c>
       <c r="U128" s="1" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V128" s="1" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W128" s="1">
@@ -14766,10 +15136,13 @@
       </c>
       <c r="AG128" s="1"/>
       <c r="AH128" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>32</v>
       </c>
-      <c r="AI128" s="1"/>
+      <c r="AI128" s="1">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AJ128" s="1"/>
       <c r="AK128" s="1"/>
       <c r="AL128" s="1"/>
@@ -14813,7 +15186,7 @@
         <v>11</v>
       </c>
       <c r="L129" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-15</v>
       </c>
       <c r="M129" s="1"/>
@@ -14826,22 +15199,22 @@
       </c>
       <c r="Q129" s="1"/>
       <c r="R129" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>-0.8</v>
       </c>
       <c r="S129" s="5">
         <v>30</v>
       </c>
       <c r="T129" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>30</v>
       </c>
       <c r="U129" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>-35</v>
       </c>
       <c r="V129" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>2.5</v>
       </c>
       <c r="W129" s="1">
@@ -14878,10 +15251,13 @@
         <v>171</v>
       </c>
       <c r="AH129" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>9</v>
       </c>
-      <c r="AI129" s="1"/>
+      <c r="AI129" s="1">
+        <f t="shared" si="28"/>
+        <v>-0.24</v>
+      </c>
       <c r="AJ129" s="1"/>
       <c r="AK129" s="1"/>
       <c r="AL129" s="1"/>
@@ -14925,7 +15301,7 @@
         <v>25</v>
       </c>
       <c r="L130" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.55799999999999983</v>
       </c>
       <c r="M130" s="1"/>
@@ -14936,7 +15312,7 @@
       <c r="P130" s="1"/>
       <c r="Q130" s="1"/>
       <c r="R130" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>5.1116000000000001</v>
       </c>
       <c r="S130" s="5">
@@ -14944,15 +15320,15 @@
         <v>31.693200000000004</v>
       </c>
       <c r="T130" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>31.693200000000004</v>
       </c>
       <c r="U130" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>9</v>
       </c>
       <c r="V130" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>2.799749589169731</v>
       </c>
       <c r="W130" s="1">
@@ -14987,10 +15363,13 @@
       </c>
       <c r="AG130" s="1"/>
       <c r="AH130" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>32</v>
       </c>
-      <c r="AI130" s="1"/>
+      <c r="AI130" s="1">
+        <f t="shared" si="28"/>
+        <v>5.1116000000000001</v>
+      </c>
       <c r="AJ130" s="1"/>
       <c r="AK130" s="1"/>
       <c r="AL130" s="1"/>
@@ -15036,7 +15415,7 @@
         <v>154</v>
       </c>
       <c r="L131" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-50</v>
       </c>
       <c r="M131" s="1"/>
@@ -15049,7 +15428,7 @@
       </c>
       <c r="Q131" s="1"/>
       <c r="R131" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>20.8</v>
       </c>
       <c r="S131" s="5">
@@ -15060,11 +15439,11 @@
         <v>56</v>
       </c>
       <c r="U131" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>3.3894230769230766</v>
       </c>
       <c r="V131" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0.69711538461538458</v>
       </c>
       <c r="W131" s="1">
@@ -15099,10 +15478,13 @@
       </c>
       <c r="AG131" s="1"/>
       <c r="AH131" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>17</v>
       </c>
-      <c r="AI131" s="1"/>
+      <c r="AI131" s="1">
+        <f t="shared" si="28"/>
+        <v>6.24</v>
+      </c>
       <c r="AJ131" s="1"/>
       <c r="AK131" s="1"/>
       <c r="AL131" s="1"/>
@@ -15148,7 +15530,7 @@
         <v>104</v>
       </c>
       <c r="L132" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-56</v>
       </c>
       <c r="M132" s="1"/>
@@ -15161,22 +15543,22 @@
       </c>
       <c r="Q132" s="1"/>
       <c r="R132" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>9.6</v>
       </c>
       <c r="S132" s="5">
         <v>50</v>
       </c>
       <c r="T132" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>50</v>
       </c>
       <c r="U132" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>5.3277083333333328</v>
       </c>
       <c r="V132" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0.11937499999999934</v>
       </c>
       <c r="W132" s="1">
@@ -15211,10 +15593,13 @@
       </c>
       <c r="AG132" s="1"/>
       <c r="AH132" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>6</v>
       </c>
-      <c r="AI132" s="1"/>
+      <c r="AI132" s="1">
+        <f t="shared" si="28"/>
+        <v>1.1519999999999999</v>
+      </c>
       <c r="AJ132" s="1"/>
       <c r="AK132" s="1"/>
       <c r="AL132" s="1"/>
@@ -15258,7 +15643,7 @@
         <v>2</v>
       </c>
       <c r="L133" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M133" s="9"/>
@@ -15269,20 +15654,20 @@
       <c r="P133" s="9"/>
       <c r="Q133" s="9"/>
       <c r="R133" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0.4</v>
       </c>
       <c r="S133" s="11"/>
       <c r="T133" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="U133" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>17.5</v>
       </c>
       <c r="V133" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>17.5</v>
       </c>
       <c r="W133" s="9">
@@ -15317,10 +15702,13 @@
       </c>
       <c r="AG133" s="9"/>
       <c r="AH133" s="1">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AI133" s="1"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AI133" s="1">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AJ133" s="1"/>
       <c r="AK133" s="1"/>
       <c r="AL133" s="1"/>
